--- a/YRIGOYEN 9115/Agosto/YRIGOYEN-EXPENSAS-Agosto.xlsx
+++ b/YRIGOYEN 9115/Agosto/YRIGOYEN-EXPENSAS-Agosto.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9115\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 9115\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77A75CC-1038-445A-8745-5DAC4C9B91B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1702E49B-5609-4A4D-B811-2BC4E5C8DAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
     <sheet name="Gastos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$113</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$114</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$O$45</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="182">
   <si>
     <t xml:space="preserve">Banco Comafi:
 Cons. Prop. Edif. Yrigoyen 9115 CUIT: 30-56975974-5
@@ -529,30 +529,12 @@
     <t>Sueldo encargada - Jimena Borges y SAC</t>
   </si>
   <si>
-    <t>PERIODO: JULIO</t>
-  </si>
-  <si>
-    <t>MES DE JULIO</t>
-  </si>
-  <si>
-    <t>Articulos de limpieza - Transf 17/07</t>
-  </si>
-  <si>
     <t xml:space="preserve">Romanatti Carlos - Escribano - Certificacion 1 firma </t>
   </si>
   <si>
-    <t>Impermeabilizacion interna tanque de reserva compartimiento cambio de dos tapas y marcos laterales - Limpieza y desinfeccion de tanques de agua potable -  cuota 3 de 4</t>
-  </si>
-  <si>
-    <t>Fumigacion Lanus 12/07</t>
-  </si>
-  <si>
     <t>Debito 14/07</t>
   </si>
   <si>
-    <t xml:space="preserve">Examen medico - Presentacion Sra. Encargada </t>
-  </si>
-  <si>
     <t>AUMENTADOS EN juli 2025</t>
   </si>
   <si>
@@ -568,10 +550,31 @@
     <t>Debito 10/07</t>
   </si>
   <si>
-    <t>VTO: 18/08</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Cutreta mariano el mes pasado pago el 14 (a nosotros nos impacto el 15) no debe tener deuda pq le cobramos incorrectamente intereses</t>
+  </si>
+  <si>
+    <t>VTO: 15/09</t>
+  </si>
+  <si>
+    <t>PERIODO: AGOSTO</t>
+  </si>
+  <si>
+    <t>MES DE AGOSTO</t>
+  </si>
+  <si>
+    <t>Impermeabilizacion interna tanque de reserva compartimiento cambio de dos tapas y marcos laterales - Limpieza y desinfeccion de tanques de agua potable -  cuota 4 de 4</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Transf 19/08</t>
+  </si>
+  <si>
+    <t>Salvatierra Nicolas - Desobstruccion de lavadero en terraza</t>
+  </si>
+  <si>
+    <t>Salvatierra Nicolas - Desobstruccion 5C</t>
+  </si>
+  <si>
+    <t>Fumigacion Lanus 14/08</t>
   </si>
 </sst>
 </file>
@@ -579,14 +582,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
-    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="33" x14ac:knownFonts="1">
     <font>
@@ -1379,10 +1382,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="232">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1402,7 +1405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1411,11 +1414,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1428,7 +1431,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1440,7 +1443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1448,15 +1451,15 @@
     <xf numFmtId="10" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1487,7 +1490,7 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1497,17 +1500,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1523,28 +1526,28 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="26" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="30" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1555,47 +1558,47 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="26" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="31" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1608,29 +1611,29 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="32" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1638,7 +1641,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1655,38 +1658,132 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1731,7 +1828,7 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1743,103 +1840,10 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2257,26 +2261,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="70" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="70" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="70" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="70" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" style="70" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="70" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="70" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" style="70" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="70" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" style="70" customWidth="1"/>
     <col min="11" max="11" width="9" style="70" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" customWidth="1"/>
+    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2285,13 +2289,13 @@
       <c r="F1" s="4"/>
       <c r="G1" s="3" t="str">
         <f>Gastos!C8</f>
-        <v>PERIODO: JULIO</v>
+        <v>PERIODO: AGOSTO</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3" t="str">
         <f>Gastos!G8</f>
-        <v>VTO: 18/08</v>
+        <v>VTO: 15/09</v>
       </c>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -2299,7 +2303,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="5"/>
     </row>
-    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
@@ -2316,7 +2320,7 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12">
@@ -2324,20 +2328,20 @@
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="170" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="172"/>
+      <c r="F3" s="171" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
+      <c r="J3" s="173"/>
       <c r="K3" s="146"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
         <v>1</v>
@@ -2345,40 +2349,40 @@
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
       <c r="E4" s="144"/>
-      <c r="F4" s="173"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="174"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="175"/>
+      <c r="F4" s="174"/>
+      <c r="G4" s="175"/>
+      <c r="H4" s="175"/>
+      <c r="I4" s="175"/>
+      <c r="J4" s="176"/>
       <c r="K4" s="146"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15"/>
-      <c r="B5" s="179">
+      <c r="B5" s="180">
         <f>C3</f>
         <v>5000000</v>
       </c>
-      <c r="C5" s="179"/>
+      <c r="C5" s="180"/>
       <c r="D5" s="16"/>
       <c r="E5" s="145">
         <v>0</v>
       </c>
-      <c r="F5" s="173"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="174"/>
-      <c r="J5" s="175"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="175"/>
+      <c r="H5" s="175"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="176"/>
       <c r="K5" s="147"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15"/>
       <c r="B6" s="17" t="s">
         <v>2</v>
@@ -2386,24 +2390,24 @@
       <c r="C6" s="18"/>
       <c r="D6" s="16"/>
       <c r="E6" s="144"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="177"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="177"/>
-      <c r="J6" s="178"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="178"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="178"/>
+      <c r="J6" s="179"/>
       <c r="K6" s="147"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15"/>
-      <c r="B7" s="179">
+      <c r="B7" s="180">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C7" s="179"/>
+      <c r="C7" s="180"/>
       <c r="D7" s="16"/>
       <c r="E7" s="18"/>
       <c r="F7" s="32"/>
@@ -2417,7 +2421,7 @@
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
     </row>
-    <row r="8" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>3</v>
       </c>
@@ -2464,7 +2468,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
         <v>1</v>
       </c>
@@ -2515,7 +2519,7 @@
         <v>550800</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2</v>
       </c>
@@ -2566,7 +2570,7 @@
         <v>146880</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <v>3</v>
       </c>
@@ -2616,7 +2620,7 @@
         <v>130558.98</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>4</v>
       </c>
@@ -2668,7 +2672,7 @@
       </c>
       <c r="P12" s="38"/>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="36">
         <v>5</v>
       </c>
@@ -2721,7 +2725,7 @@
         <v>88230</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>6</v>
       </c>
@@ -2771,7 +2775,7 @@
         <v>141644.26324766575</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="36">
         <v>7</v>
       </c>
@@ -2822,7 +2826,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>8</v>
       </c>
@@ -2875,7 +2879,7 @@
         <v>109649.99999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <v>9</v>
       </c>
@@ -2927,7 +2931,7 @@
         <v>292106.41538134078</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>10</v>
       </c>
@@ -2980,7 +2984,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>11</v>
       </c>
@@ -3033,7 +3037,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>12</v>
       </c>
@@ -3081,7 +3085,7 @@
         <v>382711.60918394738</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>13</v>
       </c>
@@ -3133,7 +3137,7 @@
         <v>145221.174</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>14</v>
       </c>
@@ -3184,7 +3188,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>15</v>
       </c>
@@ -3237,7 +3241,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>16</v>
       </c>
@@ -3289,7 +3293,7 @@
         <v>241290.69591533905</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="36">
         <v>17</v>
       </c>
@@ -3340,7 +3344,7 @@
         <v>124449.97062953994</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>18</v>
       </c>
@@ -3391,7 +3395,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <v>19</v>
       </c>
@@ -3442,7 +3446,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>20</v>
       </c>
@@ -3490,7 +3494,7 @@
         <v>386922.75547993381</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <v>21</v>
       </c>
@@ -3543,7 +3547,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>22</v>
       </c>
@@ -3596,7 +3600,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>23</v>
       </c>
@@ -3646,7 +3650,7 @@
         <v>261893.27530350833</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>24</v>
       </c>
@@ -3698,7 +3702,7 @@
         <v>524836.47025194927</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <f>A32+1</f>
         <v>25</v>
@@ -3751,7 +3755,7 @@
         <v>142063.29341615291</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <f t="shared" ref="A34:A42" si="8">A33+1</f>
         <v>26</v>
@@ -3805,7 +3809,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <f t="shared" si="8"/>
         <v>27</v>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="P35" s="87"/>
     </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <f t="shared" si="8"/>
         <v>28</v>
@@ -3912,7 +3916,7 @@
         <v>142290</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <f t="shared" si="8"/>
         <v>29</v>
@@ -3966,7 +3970,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <f t="shared" si="8"/>
         <v>30</v>
@@ -4020,7 +4024,7 @@
         <v>109649.99999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <f t="shared" si="8"/>
         <v>31</v>
@@ -4074,7 +4078,7 @@
         <v>69360</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <f t="shared" si="8"/>
         <v>32</v>
@@ -4082,7 +4086,7 @@
       <c r="B40" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="230" t="s">
+      <c r="C40" s="170" t="s">
         <v>83</v>
       </c>
       <c r="D40" s="6"/>
@@ -4125,10 +4129,10 @@
         <v>145221.174</v>
       </c>
       <c r="P40" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <f t="shared" si="8"/>
         <v>33</v>
@@ -4182,7 +4186,7 @@
         <v>126989.99999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="57">
         <f t="shared" si="8"/>
         <v>34</v>
@@ -4236,7 +4240,7 @@
         <v>187170.00000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="62"/>
       <c r="B43" s="62"/>
       <c r="C43" s="63"/>
@@ -4284,7 +4288,7 @@
       <c r="O43" s="65"/>
       <c r="P43" s="69"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G45" s="166"/>
     </row>
   </sheetData>
@@ -4301,21 +4305,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K111"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K112"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="25.42578125" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="24.5546875" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="25.44140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -4325,27 +4329,27 @@
       <c r="G1" s="72"/>
       <c r="H1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="38"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
-      <c r="G2" s="186"/>
-      <c r="H2" s="187"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D2" s="217"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="218"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="219"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="188" t="s">
+      <c r="E3" s="220" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="188"/>
-      <c r="G3" s="188"/>
-      <c r="H3" s="189"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F3" s="220"/>
+      <c r="G3" s="220"/>
+      <c r="H3" s="221"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="38"/>
       <c r="D4" s="74" t="s">
         <v>90</v>
@@ -4355,7 +4359,7 @@
       </c>
       <c r="H4" s="76"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="38"/>
       <c r="D5" s="74" t="s">
         <v>92</v>
@@ -4365,7 +4369,7 @@
       </c>
       <c r="H5" s="76"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="38"/>
       <c r="D6" s="74" t="s">
         <v>93</v>
@@ -4375,30 +4379,30 @@
       </c>
       <c r="H6" s="76"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="38"/>
       <c r="D7" s="74" t="s">
         <v>95</v>
       </c>
       <c r="H7" s="76"/>
     </row>
-    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="78" t="s">
         <v>96</v>
       </c>
       <c r="B8" s="79"/>
       <c r="C8" s="79" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D8" s="79"/>
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="79" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H8" s="81"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>97</v>
       </c>
@@ -4410,19 +4414,19 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="190" t="s">
+    <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="222" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="191"/>
-      <c r="C10" s="191"/>
-      <c r="D10" s="191"/>
-      <c r="E10" s="191"/>
-      <c r="F10" s="191"/>
-      <c r="G10" s="191"/>
-      <c r="H10" s="192"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="223"/>
+      <c r="C10" s="223"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="223"/>
+      <c r="F10" s="223"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="224"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="14"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4432,19 +4436,19 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="193" t="s">
+    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="225" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="193"/>
-      <c r="C12" s="193"/>
-      <c r="D12" s="193"/>
-      <c r="E12" s="193"/>
-      <c r="F12" s="193"/>
-      <c r="G12" s="193"/>
-      <c r="H12" s="193"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="225"/>
+      <c r="C12" s="225"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="225"/>
+      <c r="F12" s="225"/>
+      <c r="G12" s="225"/>
+      <c r="H12" s="225"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="150" t="s">
         <v>165</v>
       </c>
@@ -4458,7 +4462,7 @@
         <v>1043827.2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="150" t="s">
         <v>143</v>
       </c>
@@ -4472,7 +4476,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="152" t="s">
         <v>101</v>
       </c>
@@ -4486,7 +4490,7 @@
         <v>-227032.41</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="153" t="s">
         <v>100</v>
       </c>
@@ -4502,19 +4506,19 @@
       </c>
       <c r="I16" s="83"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="194" t="s">
+    <row r="17" spans="1:9" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="226" t="s">
         <v>162</v>
       </c>
-      <c r="B17" s="194"/>
-      <c r="C17" s="194"/>
-      <c r="D17" s="194"/>
-      <c r="E17" s="194"/>
-      <c r="F17" s="194"/>
-      <c r="G17" s="194"/>
-      <c r="H17" s="194"/>
-    </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="226"/>
+      <c r="C17" s="226"/>
+      <c r="D17" s="226"/>
+      <c r="E17" s="226"/>
+      <c r="F17" s="226"/>
+      <c r="G17" s="226"/>
+      <c r="H17" s="226"/>
+    </row>
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="85" t="s">
         <v>160</v>
       </c>
@@ -4526,7 +4530,7 @@
       <c r="G18" s="151"/>
       <c r="H18" s="82"/>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="85" t="s">
         <v>159</v>
       </c>
@@ -4538,7 +4542,7 @@
       <c r="G19" s="151"/>
       <c r="H19" s="82"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="151"/>
       <c r="B20" s="151"/>
       <c r="C20" s="151"/>
@@ -4548,7 +4552,7 @@
       <c r="G20" s="151"/>
       <c r="H20" s="82"/>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="151" t="s">
         <v>102</v>
       </c>
@@ -4563,35 +4567,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="194" t="s">
+    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="226" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="194"/>
-      <c r="C22" s="194"/>
-      <c r="D22" s="194"/>
-      <c r="E22" s="194"/>
-      <c r="F22" s="194"/>
-      <c r="G22" s="194"/>
-      <c r="H22" s="194"/>
-    </row>
-    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="226"/>
+      <c r="C22" s="226"/>
+      <c r="D22" s="226"/>
+      <c r="E22" s="226"/>
+      <c r="F22" s="226"/>
+      <c r="G22" s="226"/>
+      <c r="H22" s="226"/>
+    </row>
+    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="150" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="155" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C23" s="155"/>
       <c r="D23" s="155"/>
       <c r="E23" s="155"/>
       <c r="F23" s="155"/>
       <c r="G23" s="151"/>
-      <c r="H23" s="82">
-        <v>137308.57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H23" s="231">
+        <v>92476.76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="150" t="s">
         <v>151</v>
       </c>
@@ -4608,7 +4612,7 @@
         <v>69862.55</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="150" t="s">
         <v>105</v>
       </c>
@@ -4621,27 +4625,27 @@
       <c r="E25" s="155"/>
       <c r="F25" s="155"/>
       <c r="G25" s="151"/>
-      <c r="H25" s="82">
-        <v>7762.51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H25" s="231">
+        <v>5219.1400000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="150" t="s">
         <v>157</v>
       </c>
       <c r="B26" s="151" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C26" s="155"/>
       <c r="D26" s="155"/>
       <c r="E26" s="155"/>
       <c r="F26" s="155"/>
       <c r="G26" s="151"/>
-      <c r="H26" s="82">
-        <v>714361.65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H26" s="231">
+        <v>480315.88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="150"/>
       <c r="B27" s="151"/>
       <c r="C27" s="155"/>
@@ -4653,7 +4657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="154" t="s">
         <v>106</v>
       </c>
@@ -4665,22 +4669,22 @@
       <c r="G28" s="154"/>
       <c r="H28" s="84">
         <f>SUM(H23:H27)</f>
-        <v>929295.28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="184" t="s">
+        <v>647874.33000000007</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="216" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="184"/>
-      <c r="C29" s="184"/>
-      <c r="D29" s="184"/>
-      <c r="E29" s="184"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="184"/>
-      <c r="H29" s="184"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="216"/>
+      <c r="C29" s="216"/>
+      <c r="D29" s="216"/>
+      <c r="E29" s="216"/>
+      <c r="F29" s="216"/>
+      <c r="G29" s="216"/>
+      <c r="H29" s="216"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="151" t="s">
         <v>108</v>
       </c>
@@ -4688,16 +4692,15 @@
       <c r="C30" s="151"/>
       <c r="D30" s="151"/>
       <c r="E30" s="151" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F30" s="151"/>
       <c r="G30" s="151"/>
-      <c r="H30" s="82">
-        <f>4203.98+290.93+200.93</f>
-        <v>4695.84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H30" s="231">
+        <v>4404.8100000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="151" t="s">
         <v>109</v>
       </c>
@@ -4707,16 +4710,16 @@
       <c r="C31" s="151"/>
       <c r="D31" s="151"/>
       <c r="E31" s="151" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F31" s="151"/>
       <c r="G31" s="151"/>
-      <c r="H31" s="82">
+      <c r="H31" s="231">
         <v>1073579.78</v>
       </c>
       <c r="I31" s="87"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="156" t="s">
         <v>111</v>
       </c>
@@ -4728,11 +4731,11 @@
       <c r="E32" s="151"/>
       <c r="F32" s="151"/>
       <c r="G32" s="151"/>
-      <c r="H32" s="82">
-        <v>203720.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H32" s="231">
+        <v>197929.65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="154" t="s">
         <v>100</v>
       </c>
@@ -4744,22 +4747,22 @@
       <c r="G33" s="154"/>
       <c r="H33" s="157">
         <f>SUM(H30:H32)</f>
-        <v>1281996.02</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="184" t="s">
+        <v>1275914.24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="216" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="184"/>
-      <c r="C34" s="184"/>
-      <c r="D34" s="184"/>
-      <c r="E34" s="184"/>
-      <c r="F34" s="184"/>
-      <c r="G34" s="184"/>
-      <c r="H34" s="184"/>
-    </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="216"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="85"/>
       <c r="B35" s="158"/>
       <c r="C35" s="151"/>
@@ -4769,7 +4772,7 @@
       <c r="G35" s="151"/>
       <c r="H35" s="82"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="85" t="s">
         <v>158</v>
       </c>
@@ -4779,13 +4782,13 @@
       <c r="E36" s="151"/>
       <c r="F36" s="151"/>
       <c r="G36" s="151"/>
-      <c r="H36" s="82">
+      <c r="H36" s="231">
         <v>140000</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="85" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B37" s="159"/>
       <c r="C37" s="85"/>
@@ -4793,294 +4796,298 @@
       <c r="E37" s="85"/>
       <c r="F37" s="85"/>
       <c r="G37" s="85"/>
-      <c r="H37" s="82">
-        <v>40000</v>
+      <c r="H37" s="231">
+        <v>45000</v>
       </c>
       <c r="J37" s="87"/>
     </row>
-    <row r="38" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="201" t="s">
-        <v>173</v>
-      </c>
-      <c r="B38" s="202"/>
-      <c r="C38" s="202"/>
-      <c r="D38" s="202"/>
-      <c r="E38" s="202"/>
-      <c r="F38" s="202"/>
-      <c r="G38" s="203"/>
-      <c r="H38" s="82">
-        <v>32240.45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="85" t="s">
-        <v>168</v>
-      </c>
-      <c r="B39" s="158"/>
-      <c r="C39" s="151"/>
-      <c r="D39" s="151"/>
-      <c r="E39" s="151"/>
-      <c r="F39" s="151"/>
-      <c r="G39" s="151"/>
-      <c r="H39" s="82">
-        <v>101540</v>
-      </c>
-      <c r="I39" s="148"/>
-      <c r="J39" s="204"/>
-    </row>
-    <row r="40" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="201" t="s">
-        <v>170</v>
-      </c>
-      <c r="B40" s="202"/>
-      <c r="C40" s="202"/>
-      <c r="D40" s="202"/>
-      <c r="E40" s="202"/>
-      <c r="F40" s="202"/>
-      <c r="G40" s="203"/>
-      <c r="H40" s="82">
+    <row r="38" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="194" t="s">
+        <v>179</v>
+      </c>
+      <c r="B38" s="195"/>
+      <c r="C38" s="195"/>
+      <c r="D38" s="195"/>
+      <c r="E38" s="195"/>
+      <c r="F38" s="195"/>
+      <c r="G38" s="196"/>
+      <c r="H38" s="231">
+        <v>24100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="194" t="s">
+        <v>180</v>
+      </c>
+      <c r="B39" s="195"/>
+      <c r="C39" s="195"/>
+      <c r="D39" s="195"/>
+      <c r="E39" s="195"/>
+      <c r="F39" s="195"/>
+      <c r="G39" s="196"/>
+      <c r="H39" s="231">
+        <v>24100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="85" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40" s="158"/>
+      <c r="C40" s="151"/>
+      <c r="D40" s="151"/>
+      <c r="E40" s="151"/>
+      <c r="F40" s="151"/>
+      <c r="G40" s="151"/>
+      <c r="H40" s="231">
+        <v>112550</v>
+      </c>
+      <c r="I40" s="148"/>
+      <c r="J40" s="181"/>
+    </row>
+    <row r="41" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="194" t="s">
+        <v>177</v>
+      </c>
+      <c r="B41" s="195"/>
+      <c r="C41" s="195"/>
+      <c r="D41" s="195"/>
+      <c r="E41" s="195"/>
+      <c r="F41" s="195"/>
+      <c r="G41" s="196"/>
+      <c r="H41" s="231">
         <v>741000</v>
       </c>
-      <c r="J40" s="204"/>
-    </row>
-    <row r="41" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="96" t="s">
-        <v>169</v>
-      </c>
-      <c r="B41" s="164"/>
-      <c r="C41" s="164"/>
-      <c r="D41" s="164"/>
-      <c r="E41" s="164"/>
-      <c r="F41" s="164"/>
-      <c r="G41" s="165"/>
-      <c r="H41" s="82">
+      <c r="J41" s="181"/>
+    </row>
+    <row r="42" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="96" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" s="164"/>
+      <c r="C42" s="164"/>
+      <c r="D42" s="164"/>
+      <c r="E42" s="164"/>
+      <c r="F42" s="164"/>
+      <c r="G42" s="165"/>
+      <c r="H42" s="82">
         <v>36300</v>
       </c>
-      <c r="J41" s="204"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="151" t="s">
+      <c r="J42" s="181"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="151" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="151"/>
-      <c r="C42" s="151"/>
-      <c r="D42" s="151"/>
-      <c r="E42" s="151"/>
-      <c r="F42" s="151"/>
-      <c r="G42" s="151"/>
-      <c r="H42" s="84">
-        <f>SUM(H35:H41)</f>
-        <v>1091080.45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="184" t="s">
+      <c r="B43" s="151"/>
+      <c r="C43" s="151"/>
+      <c r="D43" s="151"/>
+      <c r="E43" s="151"/>
+      <c r="F43" s="151"/>
+      <c r="G43" s="151"/>
+      <c r="H43" s="84">
+        <f>SUM(H35:H42)</f>
+        <v>1123050</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="216" t="s">
         <v>114</v>
       </c>
-      <c r="B43" s="184"/>
-      <c r="C43" s="184"/>
-      <c r="D43" s="184"/>
-      <c r="E43" s="184"/>
-      <c r="F43" s="184"/>
-      <c r="G43" s="184"/>
-      <c r="H43" s="184"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="151" t="s">
+      <c r="B44" s="216"/>
+      <c r="C44" s="216"/>
+      <c r="D44" s="216"/>
+      <c r="E44" s="216"/>
+      <c r="F44" s="216"/>
+      <c r="G44" s="216"/>
+      <c r="H44" s="216"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="151" t="s">
         <v>115</v>
       </c>
-      <c r="B44" s="151"/>
-      <c r="C44" s="151" t="s">
-        <v>167</v>
-      </c>
-      <c r="D44" s="160"/>
-      <c r="E44" s="151"/>
-      <c r="F44" s="151"/>
-      <c r="G44" s="151"/>
-      <c r="H44" s="82">
-        <v>265000</v>
-      </c>
-      <c r="J44" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="161" t="s">
-        <v>147</v>
-      </c>
       <c r="B45" s="151"/>
-      <c r="C45" s="222"/>
-      <c r="D45" s="223"/>
-      <c r="E45" s="162"/>
-      <c r="F45" s="155"/>
+      <c r="C45" s="151" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" s="160"/>
+      <c r="E45" s="151"/>
+      <c r="F45" s="151"/>
       <c r="G45" s="151"/>
       <c r="H45" s="82">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="151"/>
+        <v>265000</v>
+      </c>
+      <c r="J45" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="161" t="s">
+        <v>147</v>
+      </c>
       <c r="B46" s="151"/>
-      <c r="C46" s="155"/>
-      <c r="D46" s="155"/>
-      <c r="E46" s="155"/>
+      <c r="C46" s="202"/>
+      <c r="D46" s="203"/>
+      <c r="E46" s="162"/>
       <c r="F46" s="155"/>
       <c r="G46" s="151"/>
-      <c r="H46" s="82"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="154" t="s">
+      <c r="H46" s="231">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="151"/>
+      <c r="B47" s="151"/>
+      <c r="C47" s="155"/>
+      <c r="D47" s="155"/>
+      <c r="E47" s="155"/>
+      <c r="F47" s="155"/>
+      <c r="G47" s="151"/>
+      <c r="H47" s="82"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="154" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="154"/>
-      <c r="C47" s="154"/>
-      <c r="D47" s="154"/>
-      <c r="E47" s="154"/>
-      <c r="F47" s="154"/>
-      <c r="G47" s="154"/>
-      <c r="H47" s="84">
-        <f>SUM(H44:H46)</f>
+      <c r="B48" s="154"/>
+      <c r="C48" s="154"/>
+      <c r="D48" s="154"/>
+      <c r="E48" s="154"/>
+      <c r="F48" s="154"/>
+      <c r="G48" s="154"/>
+      <c r="H48" s="84">
+        <f>SUM(H45:H47)</f>
         <v>295000</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="195" t="s">
+    <row r="49" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="227" t="s">
         <v>116</v>
       </c>
-      <c r="B48" s="196"/>
-      <c r="C48" s="196"/>
-      <c r="D48" s="196"/>
-      <c r="E48" s="196"/>
-      <c r="F48" s="196"/>
-      <c r="G48" s="196"/>
-      <c r="H48" s="197"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="151" t="s">
+      <c r="B49" s="228"/>
+      <c r="C49" s="228"/>
+      <c r="D49" s="228"/>
+      <c r="E49" s="228"/>
+      <c r="F49" s="228"/>
+      <c r="G49" s="228"/>
+      <c r="H49" s="229"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="B49" s="151"/>
-      <c r="C49" s="151"/>
-      <c r="D49" s="151"/>
-      <c r="E49" s="151"/>
-      <c r="F49" s="151"/>
-      <c r="G49" s="151"/>
-      <c r="H49" s="82">
-        <v>60887.77</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="151"/>
       <c r="B50" s="151"/>
       <c r="C50" s="151"/>
       <c r="D50" s="151"/>
       <c r="E50" s="151"/>
       <c r="F50" s="151"/>
       <c r="G50" s="151"/>
-      <c r="H50" s="82"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="154" t="s">
+      <c r="H50" s="82">
+        <v>60887.77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="151"/>
+      <c r="B51" s="151"/>
+      <c r="C51" s="151"/>
+      <c r="D51" s="151"/>
+      <c r="E51" s="151"/>
+      <c r="F51" s="151"/>
+      <c r="G51" s="151"/>
+      <c r="H51" s="82"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="154" t="s">
         <v>106</v>
       </c>
-      <c r="B51" s="154"/>
-      <c r="C51" s="154"/>
-      <c r="D51" s="154"/>
-      <c r="E51" s="154"/>
-      <c r="F51" s="154"/>
-      <c r="G51" s="154"/>
-      <c r="H51" s="157">
-        <f>SUM(H49:H50)</f>
+      <c r="B52" s="154"/>
+      <c r="C52" s="154"/>
+      <c r="D52" s="154"/>
+      <c r="E52" s="154"/>
+      <c r="F52" s="154"/>
+      <c r="G52" s="154"/>
+      <c r="H52" s="157">
+        <f>SUM(H50:H51)</f>
         <v>60887.77</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="195" t="s">
+    <row r="53" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="227" t="s">
         <v>118</v>
       </c>
-      <c r="B52" s="196"/>
-      <c r="C52" s="196"/>
-      <c r="D52" s="196"/>
-      <c r="E52" s="196"/>
-      <c r="F52" s="196"/>
-      <c r="G52" s="196"/>
-      <c r="H52" s="197"/>
-      <c r="I52" s="87"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="85" t="s">
+      <c r="B53" s="228"/>
+      <c r="C53" s="228"/>
+      <c r="D53" s="228"/>
+      <c r="E53" s="228"/>
+      <c r="F53" s="228"/>
+      <c r="G53" s="228"/>
+      <c r="H53" s="229"/>
+      <c r="I53" s="87"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="85" t="s">
         <v>140</v>
-      </c>
-      <c r="B53" s="85"/>
-      <c r="C53" s="85"/>
-      <c r="D53" s="85"/>
-      <c r="E53" s="85"/>
-      <c r="F53" s="85" t="s">
-        <v>177</v>
-      </c>
-      <c r="G53" s="85"/>
-      <c r="H53" s="82">
-        <v>55029.24</v>
-      </c>
-      <c r="I53" s="87"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="85" t="s">
-        <v>141</v>
       </c>
       <c r="B54" s="85"/>
       <c r="C54" s="85"/>
       <c r="D54" s="85"/>
       <c r="E54" s="85"/>
       <c r="F54" s="85" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G54" s="85"/>
       <c r="H54" s="82">
-        <v>3498.02</v>
+        <v>55029.24</v>
       </c>
       <c r="I54" s="87"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="85" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="B55" s="85"/>
       <c r="C55" s="85"/>
       <c r="D55" s="85"/>
       <c r="E55" s="85"/>
-      <c r="F55" s="85"/>
+      <c r="F55" s="85" t="s">
+        <v>170</v>
+      </c>
       <c r="G55" s="85"/>
-      <c r="H55" s="84">
-        <f>SUM(H53:H54)</f>
+      <c r="H55" s="82">
+        <v>3498.02</v>
+      </c>
+      <c r="I55" s="87"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="B56" s="85"/>
+      <c r="C56" s="85"/>
+      <c r="D56" s="85"/>
+      <c r="E56" s="85"/>
+      <c r="F56" s="85"/>
+      <c r="G56" s="85"/>
+      <c r="H56" s="84">
+        <f>SUM(H54:H55)</f>
         <v>58527.259999999995</v>
       </c>
-      <c r="I55" s="87"/>
-      <c r="K55" s="83"/>
-    </row>
-    <row r="56" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="198" t="s">
+      <c r="I56" s="87"/>
+      <c r="K56" s="83"/>
+    </row>
+    <row r="57" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="204" t="s">
         <v>119</v>
       </c>
-      <c r="B56" s="199"/>
-      <c r="C56" s="199"/>
-      <c r="D56" s="199"/>
-      <c r="E56" s="199"/>
-      <c r="F56" s="199"/>
-      <c r="G56" s="199"/>
-      <c r="H56" s="200"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="86"/>
-      <c r="B57" s="86"/>
-      <c r="C57" s="86"/>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
-      <c r="H57" s="90"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B57" s="205"/>
+      <c r="C57" s="205"/>
+      <c r="D57" s="205"/>
+      <c r="E57" s="205"/>
+      <c r="F57" s="205"/>
+      <c r="G57" s="205"/>
+      <c r="H57" s="230"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="86"/>
       <c r="B58" s="86"/>
       <c r="C58" s="86"/>
@@ -5090,61 +5097,61 @@
       <c r="G58" s="86"/>
       <c r="H58" s="90"/>
     </row>
-    <row r="59" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="91" t="s">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="86"/>
+      <c r="B59" s="86"/>
+      <c r="C59" s="86"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="86"/>
+      <c r="F59" s="86"/>
+      <c r="G59" s="86"/>
+      <c r="H59" s="90"/>
+    </row>
+    <row r="60" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="A60" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="B59" s="89"/>
-      <c r="C59" s="89"/>
-      <c r="D59" s="89"/>
-      <c r="E59" s="89"/>
-      <c r="F59" s="89"/>
-      <c r="G59" s="89"/>
-      <c r="H59" s="92"/>
-    </row>
-    <row r="60" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="93"/>
-      <c r="B60" s="131"/>
-      <c r="C60" s="131"/>
-      <c r="D60" s="131"/>
-      <c r="E60" s="131"/>
-      <c r="F60" s="131"/>
-      <c r="G60" s="131"/>
-      <c r="H60" s="94"/>
-    </row>
-    <row r="61" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="91"/>
-      <c r="B61" s="89"/>
-      <c r="C61" s="89"/>
-      <c r="D61" s="89"/>
-      <c r="E61" s="89"/>
-      <c r="F61" s="89"/>
-      <c r="G61" s="89"/>
-      <c r="H61" s="92"/>
-    </row>
-    <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="198" t="s">
+      <c r="B60" s="89"/>
+      <c r="C60" s="89"/>
+      <c r="D60" s="89"/>
+      <c r="E60" s="89"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
+      <c r="H60" s="92"/>
+    </row>
+    <row r="61" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="A61" s="93"/>
+      <c r="B61" s="131"/>
+      <c r="C61" s="131"/>
+      <c r="D61" s="131"/>
+      <c r="E61" s="131"/>
+      <c r="F61" s="131"/>
+      <c r="G61" s="131"/>
+      <c r="H61" s="94"/>
+    </row>
+    <row r="62" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="91"/>
+      <c r="B62" s="89"/>
+      <c r="C62" s="89"/>
+      <c r="D62" s="89"/>
+      <c r="E62" s="89"/>
+      <c r="F62" s="89"/>
+      <c r="G62" s="89"/>
+      <c r="H62" s="92"/>
+    </row>
+    <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="204" t="s">
         <v>152</v>
       </c>
-      <c r="B62" s="199"/>
-      <c r="C62" s="199"/>
-      <c r="D62" s="199"/>
-      <c r="E62" s="199"/>
-      <c r="F62" s="199"/>
-      <c r="G62" s="199"/>
-      <c r="H62" s="127"/>
-    </row>
-    <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="91"/>
-      <c r="B63" s="89"/>
-      <c r="C63" s="89"/>
-      <c r="D63" s="89"/>
-      <c r="E63" s="89"/>
-      <c r="F63" s="89"/>
-      <c r="G63" s="89"/>
-      <c r="H63" s="92"/>
-    </row>
-    <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="205"/>
+      <c r="C63" s="205"/>
+      <c r="D63" s="205"/>
+      <c r="E63" s="205"/>
+      <c r="F63" s="205"/>
+      <c r="G63" s="205"/>
+      <c r="H63" s="127"/>
+    </row>
+    <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="91"/>
       <c r="B64" s="89"/>
       <c r="C64" s="89"/>
@@ -5154,88 +5161,86 @@
       <c r="G64" s="89"/>
       <c r="H64" s="92"/>
     </row>
-    <row r="65" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="128" t="s">
+    <row r="65" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="91"/>
+      <c r="B65" s="89"/>
+      <c r="C65" s="89"/>
+      <c r="D65" s="89"/>
+      <c r="E65" s="89"/>
+      <c r="F65" s="89"/>
+      <c r="G65" s="89"/>
+      <c r="H65" s="92"/>
+    </row>
+    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="128" t="s">
         <v>100</v>
       </c>
-      <c r="B65" s="131"/>
-      <c r="C65" s="131"/>
-      <c r="D65" s="131"/>
-      <c r="E65" s="131"/>
-      <c r="F65" s="131"/>
-      <c r="G65" s="131"/>
-      <c r="H65" s="94">
-        <f>SUM(H63:H64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="91"/>
-      <c r="B66" s="89"/>
-      <c r="C66" s="89"/>
-      <c r="D66" s="89"/>
-      <c r="E66" s="89"/>
-      <c r="F66" s="89"/>
-      <c r="G66" s="89"/>
-      <c r="H66" s="92"/>
-    </row>
-    <row r="67" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A67" s="216" t="s">
+      <c r="B66" s="131"/>
+      <c r="C66" s="131"/>
+      <c r="D66" s="131"/>
+      <c r="E66" s="131"/>
+      <c r="F66" s="131"/>
+      <c r="G66" s="131"/>
+      <c r="H66" s="94">
+        <f>SUM(H64:H65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="A67" s="91"/>
+      <c r="B67" s="89"/>
+      <c r="C67" s="89"/>
+      <c r="D67" s="89"/>
+      <c r="E67" s="89"/>
+      <c r="F67" s="89"/>
+      <c r="G67" s="89"/>
+      <c r="H67" s="92"/>
+    </row>
+    <row r="68" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A68" s="193" t="s">
         <v>120</v>
       </c>
-      <c r="B67" s="216"/>
-      <c r="C67" s="216"/>
-      <c r="D67" s="216"/>
-      <c r="E67" s="216"/>
-      <c r="F67" s="216"/>
-      <c r="G67" s="216"/>
-      <c r="H67" s="95"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="201"/>
-      <c r="B68" s="202"/>
-      <c r="C68" s="202"/>
-      <c r="D68" s="202"/>
-      <c r="E68" s="202"/>
-      <c r="F68" s="202"/>
-      <c r="G68" s="203"/>
-      <c r="H68" s="123"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="96"/>
-      <c r="B69" s="97"/>
-      <c r="C69" s="97"/>
-      <c r="D69" s="97"/>
-      <c r="E69" s="97"/>
-      <c r="F69" s="97"/>
-      <c r="G69" s="98"/>
+      <c r="B68" s="193"/>
+      <c r="C68" s="193"/>
+      <c r="D68" s="193"/>
+      <c r="E68" s="193"/>
+      <c r="F68" s="193"/>
+      <c r="G68" s="193"/>
+      <c r="H68" s="95"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="194"/>
+      <c r="B69" s="195"/>
+      <c r="C69" s="195"/>
+      <c r="D69" s="195"/>
+      <c r="E69" s="195"/>
+      <c r="F69" s="195"/>
+      <c r="G69" s="196"/>
       <c r="H69" s="123"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="217"/>
-      <c r="B70" s="218"/>
-      <c r="C70" s="218"/>
-      <c r="D70" s="218"/>
-      <c r="E70" s="218"/>
-      <c r="F70" s="218"/>
-      <c r="G70" s="219"/>
-      <c r="H70" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="132"/>
-      <c r="B71" s="133"/>
-      <c r="C71" s="133"/>
-      <c r="D71" s="133"/>
-      <c r="E71" s="133"/>
-      <c r="F71" s="133"/>
-      <c r="G71" s="134"/>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="96"/>
+      <c r="B70" s="97"/>
+      <c r="C70" s="97"/>
+      <c r="D70" s="97"/>
+      <c r="E70" s="97"/>
+      <c r="F70" s="97"/>
+      <c r="G70" s="98"/>
+      <c r="H70" s="123"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="197"/>
+      <c r="B71" s="198"/>
+      <c r="C71" s="198"/>
+      <c r="D71" s="198"/>
+      <c r="E71" s="198"/>
+      <c r="F71" s="198"/>
+      <c r="G71" s="199"/>
       <c r="H71" s="82">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="132"/>
       <c r="B72" s="133"/>
       <c r="C72" s="133"/>
@@ -5247,239 +5252,236 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="136" t="s">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="132"/>
+      <c r="B73" s="133"/>
+      <c r="C73" s="133"/>
+      <c r="D73" s="133"/>
+      <c r="E73" s="133"/>
+      <c r="F73" s="133"/>
+      <c r="G73" s="134"/>
+      <c r="H73" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="136" t="s">
         <v>100</v>
       </c>
-      <c r="B73" s="85"/>
-      <c r="C73" s="85"/>
-      <c r="D73" s="85"/>
-      <c r="E73" s="85"/>
-      <c r="F73" s="85"/>
-      <c r="G73" s="85"/>
-      <c r="H73" s="84">
-        <f>SUM(H68:H72)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="137"/>
-      <c r="B74" s="137"/>
-      <c r="C74" s="137"/>
-      <c r="D74" s="137"/>
-      <c r="E74" s="137"/>
-      <c r="F74" s="137"/>
-      <c r="G74" s="137"/>
-      <c r="H74" s="138"/>
-      <c r="I74" s="87"/>
-    </row>
-    <row r="75" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="220" t="s">
+      <c r="B74" s="85"/>
+      <c r="C74" s="85"/>
+      <c r="D74" s="85"/>
+      <c r="E74" s="85"/>
+      <c r="F74" s="85"/>
+      <c r="G74" s="85"/>
+      <c r="H74" s="84">
+        <f>SUM(H69:H73)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="137"/>
+      <c r="B75" s="137"/>
+      <c r="C75" s="137"/>
+      <c r="D75" s="137"/>
+      <c r="E75" s="137"/>
+      <c r="F75" s="137"/>
+      <c r="G75" s="137"/>
+      <c r="H75" s="138"/>
+      <c r="I75" s="87"/>
+    </row>
+    <row r="76" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="200" t="s">
         <v>121</v>
       </c>
-      <c r="B75" s="221"/>
-      <c r="C75" s="221"/>
-      <c r="D75" s="221"/>
-      <c r="E75" s="221"/>
-      <c r="F75" s="221"/>
-      <c r="G75" s="221"/>
-      <c r="H75" s="139">
-        <f>H73</f>
-        <v>0</v>
-      </c>
-      <c r="I75" s="87"/>
-    </row>
-    <row r="76" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="213" t="s">
+      <c r="B76" s="201"/>
+      <c r="C76" s="201"/>
+      <c r="D76" s="201"/>
+      <c r="E76" s="201"/>
+      <c r="F76" s="201"/>
+      <c r="G76" s="201"/>
+      <c r="H76" s="139">
+        <f>H74</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="87"/>
+    </row>
+    <row r="77" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="190" t="s">
         <v>122</v>
       </c>
-      <c r="B76" s="214"/>
-      <c r="C76" s="214"/>
-      <c r="D76" s="214"/>
-      <c r="E76" s="214"/>
-      <c r="F76" s="214"/>
-      <c r="G76" s="215"/>
-      <c r="H76" s="139">
-        <f>J79-4553581.78+20000</f>
+      <c r="B77" s="191"/>
+      <c r="C77" s="191"/>
+      <c r="D77" s="191"/>
+      <c r="E77" s="191"/>
+      <c r="F77" s="191"/>
+      <c r="G77" s="192"/>
+      <c r="H77" s="139">
+        <f>J80-4553581.78+20000</f>
         <v>466418.21999999974</v>
       </c>
-      <c r="I76" s="88"/>
-    </row>
-    <row r="77" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="224" t="s">
+      <c r="I77" s="88"/>
+    </row>
+    <row r="78" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="206" t="s">
         <v>142</v>
       </c>
-      <c r="B77" s="225"/>
-      <c r="C77" s="225"/>
-      <c r="D77" s="225"/>
-      <c r="E77" s="225"/>
-      <c r="F77" s="225"/>
-      <c r="G77" s="226"/>
-      <c r="H77" s="139"/>
-      <c r="I77" s="87"/>
-      <c r="J77" s="83"/>
-    </row>
-    <row r="78" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A78" s="220" t="s">
+      <c r="B78" s="207"/>
+      <c r="C78" s="207"/>
+      <c r="D78" s="207"/>
+      <c r="E78" s="207"/>
+      <c r="F78" s="207"/>
+      <c r="G78" s="208"/>
+      <c r="H78" s="139"/>
+      <c r="I78" s="87"/>
+      <c r="J78" s="83"/>
+    </row>
+    <row r="79" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A79" s="200" t="s">
         <v>123</v>
       </c>
-      <c r="B78" s="221"/>
-      <c r="C78" s="221"/>
-      <c r="D78" s="221"/>
-      <c r="E78" s="221"/>
-      <c r="F78" s="221"/>
-      <c r="G78" s="221"/>
-      <c r="H78" s="139">
-        <f>H59+H55+H51+H47+H42+H33+H16+H21+H28+H65</f>
-        <v>4533581.78</v>
-      </c>
-      <c r="I78" s="83"/>
-    </row>
-    <row r="79" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A79" s="227" t="s">
+      <c r="B79" s="201"/>
+      <c r="C79" s="201"/>
+      <c r="D79" s="201"/>
+      <c r="E79" s="201"/>
+      <c r="F79" s="201"/>
+      <c r="G79" s="201"/>
+      <c r="H79" s="139">
+        <f>H60+H56+H52+H48+H43+H33+H16+H21+H28+H66</f>
+        <v>4278048.5999999996</v>
+      </c>
+      <c r="I79" s="83"/>
+    </row>
+    <row r="80" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A80" s="209" t="s">
         <v>124</v>
       </c>
-      <c r="B79" s="228"/>
-      <c r="C79" s="228"/>
-      <c r="D79" s="228"/>
-      <c r="E79" s="228"/>
-      <c r="F79" s="228"/>
-      <c r="G79" s="229"/>
-      <c r="H79" s="140">
-        <f>H78+H76</f>
+      <c r="B80" s="210"/>
+      <c r="C80" s="210"/>
+      <c r="D80" s="210"/>
+      <c r="E80" s="210"/>
+      <c r="F80" s="210"/>
+      <c r="G80" s="211"/>
+      <c r="H80" s="140">
+        <f>H79+H77</f>
+        <v>4744466.8199999994</v>
+      </c>
+      <c r="I80" s="83"/>
+      <c r="J80">
         <v>5000000</v>
       </c>
-      <c r="I79" s="83"/>
-      <c r="J79">
-        <v>5000000</v>
-      </c>
-      <c r="K79" s="148"/>
-    </row>
-    <row r="80" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A80" s="227" t="s">
+      <c r="K80" s="148"/>
+    </row>
+    <row r="81" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A81" s="209" t="s">
         <v>125</v>
       </c>
-      <c r="B80" s="228"/>
-      <c r="C80" s="228"/>
-      <c r="D80" s="228"/>
-      <c r="E80" s="228"/>
-      <c r="F80" s="228"/>
-      <c r="G80" s="229"/>
-      <c r="H80" s="141">
-        <f>H75+H77</f>
-        <v>0</v>
-      </c>
-      <c r="I80" s="83"/>
-      <c r="J80" s="148"/>
-    </row>
-    <row r="81" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="180" t="s">
+      <c r="B81" s="210"/>
+      <c r="C81" s="210"/>
+      <c r="D81" s="210"/>
+      <c r="E81" s="210"/>
+      <c r="F81" s="210"/>
+      <c r="G81" s="211"/>
+      <c r="H81" s="141">
+        <f>H76+H78</f>
+        <v>0</v>
+      </c>
+      <c r="I81" s="83"/>
+      <c r="J81" s="148"/>
+    </row>
+    <row r="82" spans="1:10" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="212" t="s">
         <v>126</v>
       </c>
-      <c r="B81" s="181"/>
-      <c r="C81" s="181"/>
-      <c r="D81" s="181"/>
-      <c r="E81" s="181"/>
-      <c r="F81" s="181"/>
-      <c r="G81" s="181"/>
-      <c r="H81" s="142">
-        <f>H78+H75</f>
-        <v>4533581.78</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="182" t="s">
+      <c r="B82" s="213"/>
+      <c r="C82" s="213"/>
+      <c r="D82" s="213"/>
+      <c r="E82" s="213"/>
+      <c r="F82" s="213"/>
+      <c r="G82" s="213"/>
+      <c r="H82" s="142">
+        <f>H79+H76</f>
+        <v>4278048.5999999996</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="214" t="s">
         <v>127</v>
       </c>
-      <c r="B82" s="183"/>
-      <c r="C82" s="183"/>
-      <c r="D82" s="183"/>
-      <c r="E82" s="183"/>
-      <c r="F82" s="183"/>
-      <c r="G82" s="183"/>
-      <c r="H82" s="100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="101"/>
-      <c r="B83" s="101"/>
-      <c r="C83" s="101"/>
-      <c r="D83" s="101"/>
-      <c r="E83" s="101"/>
-      <c r="F83" s="101"/>
-      <c r="G83" s="101"/>
-      <c r="H83" s="102"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-    </row>
-    <row r="85" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A85" s="205" t="s">
+      <c r="B83" s="215"/>
+      <c r="C83" s="215"/>
+      <c r="D83" s="215"/>
+      <c r="E83" s="215"/>
+      <c r="F83" s="215"/>
+      <c r="G83" s="215"/>
+      <c r="H83" s="100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="101"/>
+      <c r="B84" s="101"/>
+      <c r="C84" s="101"/>
+      <c r="D84" s="101"/>
+      <c r="E84" s="101"/>
+      <c r="F84" s="101"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="102"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+    </row>
+    <row r="86" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A86" s="182" t="s">
         <v>128</v>
       </c>
-      <c r="B85" s="206"/>
-      <c r="C85" s="206"/>
-      <c r="D85" s="206"/>
-      <c r="E85" s="206"/>
-      <c r="F85" s="206"/>
-      <c r="G85" s="206"/>
-      <c r="H85" s="207"/>
-    </row>
-    <row r="86" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A86" s="103" t="s">
+      <c r="B86" s="183"/>
+      <c r="C86" s="183"/>
+      <c r="D86" s="183"/>
+      <c r="E86" s="183"/>
+      <c r="F86" s="183"/>
+      <c r="G86" s="183"/>
+      <c r="H86" s="184"/>
+    </row>
+    <row r="87" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A87" s="103" t="s">
         <v>129</v>
       </c>
-      <c r="B86" s="104"/>
-      <c r="C86" s="104"/>
-      <c r="D86" s="104"/>
-      <c r="E86" s="104"/>
-      <c r="F86" s="104"/>
-      <c r="G86" s="104"/>
-      <c r="H86" s="105">
+      <c r="B87" s="104"/>
+      <c r="C87" s="104"/>
+      <c r="D87" s="104"/>
+      <c r="E87" s="104"/>
+      <c r="F87" s="104"/>
+      <c r="G87" s="104"/>
+      <c r="H87" s="105">
         <v>-834604.30226353183</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="8" t="s">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B87" s="106"/>
-      <c r="C87" s="106"/>
-      <c r="D87" s="106"/>
-      <c r="E87" s="106"/>
-      <c r="F87" s="106"/>
-      <c r="G87" s="106"/>
-      <c r="H87" s="18">
+      <c r="B88" s="106"/>
+      <c r="C88" s="106"/>
+      <c r="D88" s="106"/>
+      <c r="E88" s="106"/>
+      <c r="F88" s="106"/>
+      <c r="G88" s="106"/>
+      <c r="H88" s="18">
         <f>Planilla!G43</f>
         <v>5380591.9416700006</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="107" t="s">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" s="107" t="s">
         <v>136</v>
-      </c>
-      <c r="B88" s="108"/>
-      <c r="C88" s="108"/>
-      <c r="D88" s="108"/>
-      <c r="E88" s="108"/>
-      <c r="F88" s="108"/>
-      <c r="G88" s="108"/>
-      <c r="H88" s="122">
-        <f>-H81</f>
-        <v>-4533581.78</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="107" t="s">
-        <v>131</v>
       </c>
       <c r="B89" s="108"/>
       <c r="C89" s="108"/>
@@ -5487,14 +5489,14 @@
       <c r="E89" s="108"/>
       <c r="F89" s="108"/>
       <c r="G89" s="108"/>
-      <c r="H89" s="31">
-        <f>D104</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H89" s="122">
+        <f>-H82</f>
+        <v>-4278048.5999999996</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="107" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="B90" s="108"/>
       <c r="C90" s="108"/>
@@ -5502,91 +5504,96 @@
       <c r="E90" s="108"/>
       <c r="F90" s="108"/>
       <c r="G90" s="108"/>
-      <c r="H90" s="122">
-        <f>-(3244+6707+6908+7115)</f>
-        <v>-23974</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H90" s="31">
+        <f>D105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="107" t="s">
-        <v>153</v>
-      </c>
-      <c r="B91" s="109"/>
+        <v>169</v>
+      </c>
+      <c r="B91" s="108"/>
       <c r="C91" s="108"/>
       <c r="D91" s="108"/>
       <c r="E91" s="108"/>
       <c r="F91" s="108"/>
       <c r="G91" s="108"/>
-      <c r="H91" s="130">
-        <f>-H65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A92" s="110" t="s">
+      <c r="H91" s="122">
+        <f>-(3244+6707+6908+7115)</f>
+        <v>-23974</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" s="107" t="s">
+        <v>153</v>
+      </c>
+      <c r="B92" s="109"/>
+      <c r="C92" s="108"/>
+      <c r="D92" s="108"/>
+      <c r="E92" s="108"/>
+      <c r="F92" s="108"/>
+      <c r="G92" s="108"/>
+      <c r="H92" s="130">
+        <f>-H66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="A93" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="B92" s="111"/>
-      <c r="C92" s="111"/>
-      <c r="D92" s="111"/>
-      <c r="E92" s="111"/>
-      <c r="F92" s="111"/>
-      <c r="G92" s="111"/>
-      <c r="H92" s="112">
-        <f>SUM(H86:H91)</f>
-        <v>-11568.140593531542</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="94" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="208" t="s">
+      <c r="B93" s="111"/>
+      <c r="C93" s="111"/>
+      <c r="D93" s="111"/>
+      <c r="E93" s="111"/>
+      <c r="F93" s="111"/>
+      <c r="G93" s="111"/>
+      <c r="H93" s="112">
+        <f>SUM(H87:H92)</f>
+        <v>243965.03940646909</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="185" t="s">
         <v>133</v>
       </c>
-      <c r="B94" s="209"/>
-      <c r="C94" s="209"/>
-      <c r="D94" s="209"/>
-      <c r="E94" s="209"/>
-      <c r="F94" s="209"/>
-      <c r="G94" s="209"/>
-      <c r="H94" s="210"/>
-    </row>
-    <row r="95" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="113" t="s">
+      <c r="B95" s="186"/>
+      <c r="C95" s="186"/>
+      <c r="D95" s="186"/>
+      <c r="E95" s="186"/>
+      <c r="F95" s="186"/>
+      <c r="G95" s="186"/>
+      <c r="H95" s="187"/>
+    </row>
+    <row r="96" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="B95" s="113"/>
-      <c r="C95" s="113"/>
-      <c r="D95" s="113"/>
-      <c r="E95" s="113"/>
-      <c r="F95" s="113"/>
-      <c r="G95" s="113"/>
-      <c r="H95" s="114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="6"/>
-      <c r="B96" s="115"/>
-      <c r="C96" s="108"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="18"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B96" s="113"/>
+      <c r="C96" s="113"/>
+      <c r="D96" s="113"/>
+      <c r="E96" s="113"/>
+      <c r="F96" s="113"/>
+      <c r="G96" s="113"/>
+      <c r="H96" s="114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
-      <c r="B97" s="116"/>
-      <c r="C97" s="6"/>
+      <c r="B97" s="115"/>
+      <c r="C97" s="108"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="18"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
+      <c r="B98" s="116"/>
       <c r="C98" s="6"/>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
@@ -5594,113 +5601,107 @@
       <c r="G98" s="6"/>
       <c r="H98" s="18"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="117" t="s">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="18"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="117" t="s">
         <v>132</v>
       </c>
-      <c r="B99" s="117"/>
-      <c r="C99" s="117"/>
-      <c r="D99" s="117"/>
-      <c r="E99" s="117"/>
-      <c r="F99" s="117"/>
-      <c r="G99" s="117"/>
-      <c r="H99" s="118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="124" t="s">
+      <c r="B100" s="117"/>
+      <c r="C100" s="117"/>
+      <c r="D100" s="117"/>
+      <c r="E100" s="117"/>
+      <c r="F100" s="117"/>
+      <c r="G100" s="117"/>
+      <c r="H100" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="124" t="s">
         <v>145</v>
       </c>
-      <c r="B101" s="125"/>
-      <c r="C101" s="125"/>
-      <c r="D101" s="125"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="18"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B102" s="125"/>
+      <c r="C102" s="125"/>
+      <c r="D102" s="125"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
       <c r="D103" s="18"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="119" t="s">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="18"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="B104" s="125"/>
-      <c r="C104" s="125"/>
-      <c r="D104" s="135">
-        <f>SUM(D102:D103)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="124" t="s">
+      <c r="B105" s="125"/>
+      <c r="C105" s="125"/>
+      <c r="D105" s="135">
+        <f>SUM(D103:D104)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="124" t="s">
         <v>146</v>
       </c>
-      <c r="B106" s="119"/>
-      <c r="C106" s="119"/>
-      <c r="D106" s="119"/>
-    </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="6"/>
-      <c r="B107" s="99"/>
-      <c r="C107" s="99"/>
-      <c r="D107" s="121"/>
-    </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="119"/>
+      <c r="C107" s="119"/>
+      <c r="D107" s="119"/>
+    </row>
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="126"/>
-    </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="99"/>
+      <c r="C108" s="99"/>
+      <c r="D108" s="121"/>
+    </row>
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
       <c r="D109" s="126"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
       <c r="D110" s="126"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="120" t="s">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="6"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="126"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="B111" s="120"/>
-      <c r="C111" s="211">
-        <f>SUM(D107:D110)</f>
-        <v>0</v>
-      </c>
-      <c r="D111" s="212"/>
+      <c r="B112" s="120"/>
+      <c r="C112" s="188">
+        <f>SUM(D108:D111)</f>
+        <v>0</v>
+      </c>
+      <c r="D112" s="189"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="J39:J41"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A94:H94"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A82:G82"/>
+  <mergeCells count="32">
+    <mergeCell ref="A83:G83"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="E3:H3"/>
@@ -5709,12 +5710,29 @@
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="J40:J42"/>
+    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A82:G82"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/YRIGOYEN 9115/Agosto/YRIGOYEN-EXPENSAS-Agosto.xlsx
+++ b/YRIGOYEN 9115/Agosto/YRIGOYEN-EXPENSAS-Agosto.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\YRIGOYEN 9115\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9115\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1702E49B-5609-4A4D-B811-2BC4E5C8DAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FDBE6B-3628-416F-B75C-19D30E4A617C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
     <sheet name="Gastos" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$114</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Gastos!$A$1:$H$112</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$O$45</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="184">
   <si>
     <t xml:space="preserve">Banco Comafi:
 Cons. Prop. Edif. Yrigoyen 9115 CUIT: 30-56975974-5
@@ -396,9 +396,6 @@
     <t>TOTAL GASTOS EXTRAORDINARIOS:</t>
   </si>
   <si>
-    <t>FONDO DE GASTOS ORDINARIOS</t>
-  </si>
-  <si>
     <t>TOTAL GASTOS ORDINARIOS</t>
   </si>
   <si>
@@ -442,9 +439,6 @@
   </si>
   <si>
     <t>Juan Pablo Fariña</t>
-  </si>
-  <si>
-    <t>Sol Cortina y Facundo</t>
   </si>
   <si>
     <t>Mejias Leosmari</t>
@@ -526,33 +520,12 @@
     <t>Macarena perez ruiz</t>
   </si>
   <si>
-    <t>Sueldo encargada - Jimena Borges y SAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romanatti Carlos - Escribano - Certificacion 1 firma </t>
-  </si>
-  <si>
-    <t>Debito 14/07</t>
-  </si>
-  <si>
     <t>AUMENTADOS EN juli 2025</t>
   </si>
   <si>
     <t>Punitorios mal cobrados</t>
   </si>
   <si>
-    <t>Debito 04/07</t>
-  </si>
-  <si>
-    <t>Debito 23/07</t>
-  </si>
-  <si>
-    <t>Debito 10/07</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Cutreta mariano el mes pasado pago el 14 (a nosotros nos impacto el 15) no debe tener deuda pq le cobramos incorrectamente intereses</t>
-  </si>
-  <si>
     <t>VTO: 15/09</t>
   </si>
   <si>
@@ -571,10 +544,43 @@
     <t>Salvatierra Nicolas - Desobstruccion de lavadero en terraza</t>
   </si>
   <si>
-    <t>Salvatierra Nicolas - Desobstruccion 5C</t>
-  </si>
-  <si>
-    <t>Fumigacion Lanus 14/08</t>
+    <t xml:space="preserve">Sueldo encargada - Jimena Borges </t>
+  </si>
+  <si>
+    <t>Debito 07/08</t>
+  </si>
+  <si>
+    <t>Debito 12/08</t>
+  </si>
+  <si>
+    <t>Fumigacion Lanus 12/08</t>
+  </si>
+  <si>
+    <t>Debito 13/08</t>
+  </si>
+  <si>
+    <t>Debito 14/08</t>
+  </si>
+  <si>
+    <t>Salvatierra Nicolas - Desobstruccion 5C colectora</t>
+  </si>
+  <si>
+    <t>Debito 21/08</t>
+  </si>
+  <si>
+    <t>Debito 22/08</t>
+  </si>
+  <si>
+    <t>Valeria</t>
+  </si>
+  <si>
+    <t>Lucas damian Cabrera</t>
+  </si>
+  <si>
+    <t>FONDO DE GASTOS ORDINARIOS - ARREGLO TERRAZA</t>
+  </si>
+  <si>
+    <t>Administracion Honorarios traspaso</t>
   </si>
 </sst>
 </file>
@@ -582,14 +588,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="33" x14ac:knownFonts="1">
     <font>
@@ -1382,10 +1388,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1405,7 +1411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1414,11 +1420,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1431,7 +1437,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1443,7 +1449,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1451,15 +1457,15 @@
     <xf numFmtId="10" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1490,7 +1496,7 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1500,17 +1506,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1526,28 +1532,28 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="26" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="30" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="28" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1558,47 +1564,47 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="26" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="26" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="26" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="26" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="31" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1611,29 +1617,29 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="32" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="32" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1641,7 +1647,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1652,47 +1658,106 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1714,10 +1779,10 @@
     <xf numFmtId="0" fontId="23" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1733,15 +1798,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1762,12 +1818,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1792,58 +1842,7 @@
     <xf numFmtId="0" fontId="30" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2260,27 +2259,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="70" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="70" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" style="70" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="70" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="70" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="70" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="70" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="70" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="70" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="70" customWidth="1"/>
     <col min="11" max="11" width="9" style="70" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="14.44140625" customWidth="1"/>
-    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2303,7 +2302,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="5"/>
     </row>
-    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
@@ -2320,28 +2319,28 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12">
-        <v>5000000</v>
+        <v>5482071.4900000002</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="171" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="173"/>
+      <c r="F3" s="168" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="169"/>
+      <c r="H3" s="169"/>
+      <c r="I3" s="169"/>
+      <c r="J3" s="170"/>
       <c r="K3" s="146"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
         <v>1</v>
@@ -2349,40 +2348,40 @@
       <c r="C4" s="6"/>
       <c r="D4" s="8"/>
       <c r="E4" s="144"/>
-      <c r="F4" s="174"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="176"/>
+      <c r="F4" s="171"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="172"/>
+      <c r="I4" s="172"/>
+      <c r="J4" s="173"/>
       <c r="K4" s="146"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
-      <c r="B5" s="180">
+      <c r="B5" s="177">
         <f>C3</f>
-        <v>5000000</v>
-      </c>
-      <c r="C5" s="180"/>
+        <v>5482071.4900000002</v>
+      </c>
+      <c r="C5" s="177"/>
       <c r="D5" s="16"/>
       <c r="E5" s="145">
         <v>0</v>
       </c>
-      <c r="F5" s="174"/>
-      <c r="G5" s="175"/>
-      <c r="H5" s="175"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="176"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="173"/>
       <c r="K5" s="147"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15"/>
       <c r="B6" s="17" t="s">
         <v>2</v>
@@ -2390,24 +2389,24 @@
       <c r="C6" s="18"/>
       <c r="D6" s="16"/>
       <c r="E6" s="144"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="178"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="178"/>
-      <c r="J6" s="179"/>
+      <c r="F6" s="174"/>
+      <c r="G6" s="175"/>
+      <c r="H6" s="175"/>
+      <c r="I6" s="175"/>
+      <c r="J6" s="176"/>
       <c r="K6" s="147"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
-      <c r="B7" s="180">
+      <c r="B7" s="177">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="C7" s="180"/>
+      <c r="C7" s="177"/>
       <c r="D7" s="16"/>
       <c r="E7" s="18"/>
       <c r="F7" s="32"/>
@@ -2421,7 +2420,7 @@
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
     </row>
-    <row r="8" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>3</v>
       </c>
@@ -2453,7 +2452,7 @@
         <v>12</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L8" s="20" t="s">
         <v>13</v>
@@ -2468,7 +2467,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>1</v>
       </c>
@@ -2485,8 +2484,7 @@
       <c r="F9" s="31">
         <v>540000</v>
       </c>
-      <c r="G9" s="167">
-        <f>F9</f>
+      <c r="G9" s="165">
         <v>540000</v>
       </c>
       <c r="H9" s="32">
@@ -2504,7 +2502,7 @@
       <c r="K9" s="32"/>
       <c r="L9" s="33">
         <f>B$5*E9</f>
-        <v>540000</v>
+        <v>592063.72091999999</v>
       </c>
       <c r="M9" s="33">
         <f>B$7*E9</f>
@@ -2512,14 +2510,14 @@
       </c>
       <c r="N9" s="34">
         <f>H9+I9-J9+K9+L9+M9</f>
-        <v>540000</v>
+        <v>592063.72091999999</v>
       </c>
       <c r="O9" s="35">
         <f>N9*2% + N9</f>
-        <v>550800</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>603904.99533840001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>2</v>
       </c>
@@ -2555,7 +2553,7 @@
       <c r="K10" s="32"/>
       <c r="L10" s="33">
         <f t="shared" ref="L10:L42" si="3">B$5*E10</f>
-        <v>144000</v>
+        <v>157883.65891200001</v>
       </c>
       <c r="M10" s="33">
         <f t="shared" ref="M10:M42" si="4">B$7*E10</f>
@@ -2563,14 +2561,14 @@
       </c>
       <c r="N10" s="34">
         <f t="shared" ref="N10:N42" si="5">H10+I10-J10+K10+L10+M10</f>
-        <v>144000</v>
+        <v>157883.65891200001</v>
       </c>
       <c r="O10" s="35">
         <f t="shared" ref="O10:O42" si="6">N10*2% + N10</f>
-        <v>146880</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>161041.33209024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36">
         <v>3</v>
       </c>
@@ -2585,10 +2583,10 @@
         <v>2.5600000000000001E-2</v>
       </c>
       <c r="F11" s="31">
-        <v>130507</v>
+        <v>128000.82</v>
       </c>
       <c r="G11" s="149">
-        <v>130508</v>
+        <v>130560</v>
       </c>
       <c r="H11" s="32">
         <f t="shared" si="0"/>
@@ -2600,12 +2598,12 @@
       </c>
       <c r="J11" s="32">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2559.179999999993</v>
       </c>
       <c r="K11" s="32"/>
       <c r="L11" s="33">
         <f t="shared" si="3"/>
-        <v>128000</v>
+        <v>140341.03014400002</v>
       </c>
       <c r="M11" s="33">
         <f t="shared" si="4"/>
@@ -2613,14 +2611,14 @@
       </c>
       <c r="N11" s="34">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>127999</v>
+        <v>137781.85014400003</v>
       </c>
       <c r="O11" s="35">
         <f t="shared" si="6"/>
-        <v>130558.98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>140537.48714688001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>4</v>
       </c>
@@ -2635,19 +2633,18 @@
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="F12" s="31">
-        <v>107499.99999999999</v>
+        <v>109649.99999999999</v>
       </c>
       <c r="G12" s="149">
-        <f>F12</f>
-        <v>107499.99999999999</v>
+        <v>107500</v>
       </c>
       <c r="H12" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2149.9999999999854</v>
       </c>
       <c r="I12" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>64.499999999999559</v>
       </c>
       <c r="J12" s="32">
         <f t="shared" si="2"/>
@@ -2656,7 +2653,7 @@
       <c r="K12" s="32"/>
       <c r="L12" s="33">
         <f t="shared" si="3"/>
-        <v>107499.99999999999</v>
+        <v>117864.537035</v>
       </c>
       <c r="M12" s="33">
         <f t="shared" si="4"/>
@@ -2664,15 +2661,15 @@
       </c>
       <c r="N12" s="34">
         <f t="shared" si="5"/>
-        <v>107499.99999999999</v>
+        <v>120079.03703499999</v>
       </c>
       <c r="O12" s="35">
         <f t="shared" si="6"/>
-        <v>109649.99999999999</v>
+        <v>122480.61777569998</v>
       </c>
       <c r="P12" s="38"/>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
         <v>5</v>
       </c>
@@ -2683,7 +2680,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="E13" s="30">
         <v>1.7299999999999999E-2</v>
@@ -2692,16 +2689,15 @@
         <v>88230</v>
       </c>
       <c r="G13" s="149">
-        <f>F13</f>
-        <v>88230</v>
+        <v>86500</v>
       </c>
       <c r="H13" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1730</v>
       </c>
       <c r="I13" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>51.9</v>
       </c>
       <c r="J13" s="32">
         <f t="shared" si="2"/>
@@ -2710,7 +2706,7 @@
       <c r="K13" s="32"/>
       <c r="L13" s="33">
         <f t="shared" si="3"/>
-        <v>86500</v>
+        <v>94839.836777000004</v>
       </c>
       <c r="M13" s="33">
         <f t="shared" si="4"/>
@@ -2718,14 +2714,14 @@
       </c>
       <c r="N13" s="34">
         <f t="shared" si="5"/>
-        <v>86500</v>
+        <v>96621.736776999998</v>
       </c>
       <c r="O13" s="35">
         <f t="shared" si="6"/>
-        <v>88230</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>98554.171512539993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>6</v>
       </c>
@@ -2740,7 +2736,7 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F14" s="31">
-        <v>139366.92475261347</v>
+        <v>138866.92475261347</v>
       </c>
       <c r="G14" s="149">
         <v>140000</v>
@@ -2755,12 +2751,12 @@
       </c>
       <c r="J14" s="32">
         <f t="shared" si="2"/>
-        <v>633.07524738652864</v>
+        <v>1133.0752473865286</v>
       </c>
       <c r="K14" s="32"/>
       <c r="L14" s="33">
         <f t="shared" si="3"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="M14" s="33">
         <f t="shared" si="4"/>
@@ -2768,14 +2764,14 @@
       </c>
       <c r="N14" s="34">
         <f t="shared" si="5"/>
-        <v>138866.92475261347</v>
+        <v>151816.71932361348</v>
       </c>
       <c r="O14" s="35">
         <f t="shared" si="6"/>
-        <v>141644.26324766575</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>154853.05371008575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
         <v>7</v>
       </c>
@@ -2811,7 +2807,7 @@
       <c r="K15" s="32"/>
       <c r="L15" s="33">
         <f t="shared" si="3"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="M15" s="33">
         <f t="shared" si="4"/>
@@ -2819,14 +2815,14 @@
       </c>
       <c r="N15" s="34">
         <f t="shared" si="5"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="O15" s="35">
         <f t="shared" si="6"/>
-        <v>126989.99999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>139233.65170302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>8</v>
       </c>
@@ -2837,7 +2833,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E16" s="30">
         <v>2.1499999999999998E-2</v>
@@ -2864,7 +2860,7 @@
       <c r="K16" s="32"/>
       <c r="L16" s="33">
         <f t="shared" si="3"/>
-        <v>107499.99999999999</v>
+        <v>117864.537035</v>
       </c>
       <c r="M16" s="33">
         <f t="shared" si="4"/>
@@ -2872,14 +2868,14 @@
       </c>
       <c r="N16" s="34">
         <f t="shared" si="5"/>
-        <v>107499.99999999999</v>
+        <v>117864.537035</v>
       </c>
       <c r="O16" s="35">
         <f t="shared" si="6"/>
-        <v>109649.99999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>120221.8277757</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
         <v>9</v>
       </c>
@@ -2890,24 +2886,22 @@
         <v>34</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E17" s="30">
         <v>1.3599999999999999E-2</v>
       </c>
       <c r="F17" s="31">
-        <v>262018.28991180353</v>
-      </c>
-      <c r="G17" s="149">
-        <v>50000</v>
-      </c>
+        <v>286378.8386091576</v>
+      </c>
+      <c r="G17" s="149"/>
       <c r="H17" s="32">
         <f t="shared" si="0"/>
-        <v>212018.28991180353</v>
+        <v>286378.8386091576</v>
       </c>
       <c r="I17" s="32">
         <f t="shared" si="1"/>
-        <v>6360.5486973541056</v>
+        <v>8591.3651582747279</v>
       </c>
       <c r="J17" s="32">
         <f t="shared" si="2"/>
@@ -2916,7 +2910,7 @@
       <c r="K17" s="32"/>
       <c r="L17" s="33">
         <f t="shared" si="3"/>
-        <v>68000</v>
+        <v>74556.172263999993</v>
       </c>
       <c r="M17" s="33">
         <f t="shared" si="4"/>
@@ -2924,14 +2918,14 @@
       </c>
       <c r="N17" s="34">
         <f t="shared" si="5"/>
-        <v>286378.8386091576</v>
+        <v>369526.3760314323</v>
       </c>
       <c r="O17" s="35">
         <f t="shared" si="6"/>
-        <v>292106.41538134078</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>376916.90355206095</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>10</v>
       </c>
@@ -2939,20 +2933,20 @@
         <v>35</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E18" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F18" s="31">
-        <v>139500</v>
+        <v>142290</v>
       </c>
       <c r="G18" s="149">
         <f t="shared" ref="G18:G23" si="7">F18</f>
-        <v>139500</v>
+        <v>142290</v>
       </c>
       <c r="H18" s="32">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
@@ -2969,7 +2963,7 @@
       <c r="K18" s="32"/>
       <c r="L18" s="33">
         <f t="shared" si="3"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="M18" s="33">
         <f t="shared" si="4"/>
@@ -2977,14 +2971,14 @@
       </c>
       <c r="N18" s="34">
         <f t="shared" si="5"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="O18" s="35">
         <f t="shared" si="6"/>
-        <v>142290</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>156008.79046242</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="36">
         <v>11</v>
       </c>
@@ -2995,7 +2989,7 @@
         <v>37</v>
       </c>
       <c r="D19" s="163" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E19" s="30">
         <v>2.4899999999999999E-2</v>
@@ -3022,7 +3016,7 @@
       <c r="K19" s="32"/>
       <c r="L19" s="33">
         <f t="shared" si="3"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="M19" s="33">
         <f t="shared" si="4"/>
@@ -3030,14 +3024,14 @@
       </c>
       <c r="N19" s="34">
         <f t="shared" si="5"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="O19" s="35">
         <f t="shared" si="6"/>
-        <v>126989.99999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>139233.65170302</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>12</v>
       </c>
@@ -3052,16 +3046,18 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F20" s="31">
-        <v>186123.747557536</v>
-      </c>
-      <c r="G20" s="149"/>
+        <v>375207.45998426212</v>
+      </c>
+      <c r="G20" s="149">
+        <v>190000</v>
+      </c>
       <c r="H20" s="32">
         <f t="shared" si="0"/>
-        <v>186123.747557536</v>
+        <v>185207.45998426212</v>
       </c>
       <c r="I20" s="32">
         <f t="shared" si="1"/>
-        <v>5583.7124267260797</v>
+        <v>5556.2237995278638</v>
       </c>
       <c r="J20" s="32">
         <f t="shared" si="2"/>
@@ -3070,7 +3066,7 @@
       <c r="K20" s="32"/>
       <c r="L20" s="33">
         <f t="shared" si="3"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="M20" s="33">
         <f t="shared" si="4"/>
@@ -3078,14 +3074,14 @@
       </c>
       <c r="N20" s="34">
         <f t="shared" si="5"/>
-        <v>375207.45998426212</v>
+        <v>391955.70746678999</v>
       </c>
       <c r="O20" s="35">
         <f t="shared" si="6"/>
-        <v>382711.60918394738</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>399794.82161612576</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>13</v>
       </c>
@@ -3096,24 +3092,24 @@
         <v>41</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E21" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F21" s="31">
-        <v>142290</v>
+        <v>145309.10922000001</v>
       </c>
       <c r="G21" s="149">
-        <v>139500</v>
+        <v>145222</v>
       </c>
       <c r="H21" s="32">
         <f t="shared" si="0"/>
-        <v>2790</v>
+        <v>87.109220000013011</v>
       </c>
       <c r="I21" s="32">
         <f t="shared" si="1"/>
-        <v>83.7</v>
+        <v>2.6132766000003902</v>
       </c>
       <c r="J21" s="32">
         <f t="shared" si="2"/>
@@ -3122,7 +3118,7 @@
       <c r="K21" s="32"/>
       <c r="L21" s="33">
         <f t="shared" si="3"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="M21" s="33">
         <f t="shared" si="4"/>
@@ -3130,14 +3126,14 @@
       </c>
       <c r="N21" s="34">
         <f t="shared" si="5"/>
-        <v>142373.70000000001</v>
+        <v>153039.51706760001</v>
       </c>
       <c r="O21" s="35">
         <f t="shared" si="6"/>
-        <v>145221.174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>156100.30740895201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
         <v>14</v>
       </c>
@@ -3173,7 +3169,7 @@
       <c r="K22" s="32"/>
       <c r="L22" s="33">
         <f t="shared" si="3"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="M22" s="33">
         <f t="shared" si="4"/>
@@ -3181,14 +3177,14 @@
       </c>
       <c r="N22" s="34">
         <f t="shared" si="5"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="O22" s="35">
         <f t="shared" si="6"/>
-        <v>126989.99999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>139233.65170302</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="36">
         <v>15</v>
       </c>
@@ -3199,7 +3195,7 @@
         <v>45</v>
       </c>
       <c r="D23" s="47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E23" s="30">
         <v>3.6700000000000003E-2</v>
@@ -3226,7 +3222,7 @@
       <c r="K23" s="32"/>
       <c r="L23" s="33">
         <f t="shared" si="3"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="M23" s="33">
         <f t="shared" si="4"/>
@@ -3234,14 +3230,14 @@
       </c>
       <c r="N23" s="34">
         <f t="shared" si="5"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="O23" s="35">
         <f t="shared" si="6"/>
-        <v>187170.00000000003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205215.86415666004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <v>16</v>
       </c>
@@ -3252,24 +3248,24 @@
         <v>47</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E24" s="30">
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F24" s="31">
-        <v>233732.52990228351</v>
+        <v>236559.50579935202</v>
       </c>
       <c r="G24" s="149">
         <v>139500</v>
       </c>
       <c r="H24" s="32">
         <f t="shared" si="0"/>
-        <v>94232.52990228351</v>
+        <v>97059.505799352017</v>
       </c>
       <c r="I24" s="32">
         <f t="shared" si="1"/>
-        <v>2826.9758970685052</v>
+        <v>2911.7851739805606</v>
       </c>
       <c r="J24" s="32">
         <f t="shared" si="2"/>
@@ -3278,7 +3274,7 @@
       <c r="K24" s="32"/>
       <c r="L24" s="33">
         <f t="shared" si="3"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="M24" s="33">
         <f t="shared" si="4"/>
@@ -3286,14 +3282,17 @@
       </c>
       <c r="N24" s="34">
         <f t="shared" si="5"/>
-        <v>236559.50579935202</v>
+        <v>252921.08554433257</v>
       </c>
       <c r="O24" s="35">
         <f t="shared" si="6"/>
-        <v>241290.69591533905</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>257979.50725521921</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="36">
         <v>17</v>
       </c>
@@ -3308,11 +3307,10 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F25" s="31">
-        <v>124499.77512699996</v>
+        <v>122009.77512699994</v>
       </c>
       <c r="G25" s="149">
-        <f>126990</f>
-        <v>126990</v>
+        <v>124500</v>
       </c>
       <c r="H25" s="32">
         <f t="shared" si="0"/>
@@ -3324,12 +3322,12 @@
       </c>
       <c r="J25" s="32">
         <f t="shared" si="2"/>
-        <v>2490.2248730000429</v>
+        <v>2490.2248730000574</v>
       </c>
       <c r="K25" s="32"/>
       <c r="L25" s="33">
         <f t="shared" si="3"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="M25" s="33">
         <f t="shared" si="4"/>
@@ -3337,14 +3335,14 @@
       </c>
       <c r="N25" s="34">
         <f t="shared" si="5"/>
-        <v>122009.77512699994</v>
+        <v>134013.35522799994</v>
       </c>
       <c r="O25" s="35">
         <f t="shared" si="6"/>
-        <v>124449.97062953994</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>136693.62233255993</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <v>18</v>
       </c>
@@ -3380,7 +3378,7 @@
       <c r="K26" s="32"/>
       <c r="L26" s="33">
         <f t="shared" si="3"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="M26" s="33">
         <f t="shared" si="4"/>
@@ -3388,14 +3386,14 @@
       </c>
       <c r="N26" s="34">
         <f t="shared" si="5"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="O26" s="35">
         <f t="shared" si="6"/>
-        <v>187170.00000000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205215.86415666004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="36">
         <v>19</v>
       </c>
@@ -3431,7 +3429,7 @@
       <c r="K27" s="32"/>
       <c r="L27" s="33">
         <f t="shared" si="3"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="M27" s="33">
         <f t="shared" si="4"/>
@@ -3439,14 +3437,14 @@
       </c>
       <c r="N27" s="34">
         <f t="shared" si="5"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="O27" s="35">
         <f t="shared" si="6"/>
-        <v>142290</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>156008.79046242</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="36">
         <v>20</v>
       </c>
@@ -3461,16 +3459,16 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F28" s="31">
-        <v>247413.62600412511</v>
+        <v>379336.03478424886</v>
       </c>
       <c r="G28" s="149"/>
       <c r="H28" s="54">
         <f t="shared" si="0"/>
-        <v>247413.62600412511</v>
+        <v>379336.03478424886</v>
       </c>
       <c r="I28" s="32">
         <f t="shared" si="1"/>
-        <v>7422.4087801237529</v>
+        <v>11380.081043527465</v>
       </c>
       <c r="J28" s="32">
         <f t="shared" si="2"/>
@@ -3479,7 +3477,7 @@
       <c r="K28" s="32"/>
       <c r="L28" s="33">
         <f t="shared" si="3"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="M28" s="33">
         <f t="shared" si="4"/>
@@ -3487,14 +3485,14 @@
       </c>
       <c r="N28" s="34">
         <f t="shared" si="5"/>
-        <v>379336.03478424886</v>
+        <v>527219.69592877629</v>
       </c>
       <c r="O28" s="35">
         <f t="shared" si="6"/>
-        <v>386922.75547993381</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>537764.08984735177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="36">
         <v>21</v>
       </c>
@@ -3505,7 +3503,7 @@
         <v>57</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E29" s="30">
         <v>3.6700000000000003E-2</v>
@@ -3532,7 +3530,7 @@
       <c r="K29" s="32"/>
       <c r="L29" s="33">
         <f t="shared" si="3"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="M29" s="33">
         <f t="shared" si="4"/>
@@ -3540,14 +3538,14 @@
       </c>
       <c r="N29" s="34">
         <f t="shared" si="5"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="O29" s="35">
         <f t="shared" si="6"/>
-        <v>187170.00000000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205215.86415666004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>22</v>
       </c>
@@ -3585,7 +3583,7 @@
       <c r="K30" s="32"/>
       <c r="L30" s="33">
         <f t="shared" si="3"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="M30" s="33">
         <f t="shared" si="4"/>
@@ -3593,14 +3591,14 @@
       </c>
       <c r="N30" s="34">
         <f t="shared" si="5"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="O30" s="35">
         <f t="shared" si="6"/>
-        <v>142290</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>156008.79046242</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
         <v>23</v>
       </c>
@@ -3615,18 +3613,16 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F31" s="31">
-        <v>526804.93499286915</v>
-      </c>
-      <c r="G31" s="149">
-        <v>398399</v>
-      </c>
+        <v>256758.11304265523</v>
+      </c>
+      <c r="G31" s="149"/>
       <c r="H31" s="32">
         <f t="shared" si="0"/>
-        <v>128405.93499286915</v>
+        <v>256758.11304265523</v>
       </c>
       <c r="I31" s="32">
         <f t="shared" si="1"/>
-        <v>3852.1780497860746</v>
+        <v>7702.7433912796569</v>
       </c>
       <c r="J31" s="32">
         <f t="shared" si="2"/>
@@ -3635,7 +3631,7 @@
       <c r="K31" s="32"/>
       <c r="L31" s="33">
         <f t="shared" si="3"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="M31" s="33">
         <f t="shared" si="4"/>
@@ -3643,14 +3639,14 @@
       </c>
       <c r="N31" s="34">
         <f t="shared" si="5"/>
-        <v>256758.11304265523</v>
+        <v>400964.43653493491</v>
       </c>
       <c r="O31" s="35">
         <f t="shared" si="6"/>
-        <v>261893.27530350833</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+        <v>408983.72526563361</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="36">
         <v>24</v>
       </c>
@@ -3661,24 +3657,24 @@
         <v>64</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E32" s="30">
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F32" s="18">
-        <v>672579.4554082898</v>
+        <v>514545.5590705385</v>
       </c>
       <c r="G32" s="149">
-        <v>351176</v>
+        <v>350000</v>
       </c>
       <c r="H32" s="32">
         <f t="shared" si="0"/>
-        <v>321403.4554082898</v>
+        <v>164545.5590705385</v>
       </c>
       <c r="I32" s="32">
         <f t="shared" si="1"/>
-        <v>9642.1036622486936</v>
+        <v>4936.3667721161546</v>
       </c>
       <c r="J32" s="32">
         <f t="shared" si="2"/>
@@ -3687,7 +3683,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="33">
         <f t="shared" si="3"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="M32" s="33">
         <f t="shared" si="4"/>
@@ -3695,14 +3691,14 @@
       </c>
       <c r="N32" s="34">
         <f t="shared" si="5"/>
-        <v>514545.5590705385</v>
+        <v>370673.94952565467</v>
       </c>
       <c r="O32" s="35">
         <f t="shared" si="6"/>
-        <v>524836.47025194927</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>378087.42851616774</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <f>A32+1</f>
         <v>25</v>
@@ -3720,27 +3716,27 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F33" s="126">
-        <v>135277.73864328716</v>
+        <v>146258.89221863748</v>
       </c>
       <c r="G33" s="149">
-        <v>135500</v>
+        <v>139500</v>
       </c>
       <c r="H33" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6758.8922186374839</v>
       </c>
       <c r="I33" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>202.76676655912451</v>
       </c>
       <c r="J33" s="32">
         <f t="shared" si="2"/>
-        <v>222.26135671284283</v>
+        <v>0</v>
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="33">
         <f t="shared" si="3"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="M33" s="33">
         <f t="shared" si="4"/>
@@ -3748,14 +3744,14 @@
       </c>
       <c r="N33" s="34">
         <f t="shared" si="5"/>
-        <v>139277.73864328716</v>
+        <v>159911.45355619662</v>
       </c>
       <c r="O33" s="35">
         <f t="shared" si="6"/>
-        <v>142063.29341615291</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>163109.68262732055</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <f t="shared" ref="A34:A42" si="8">A33+1</f>
         <v>26</v>
@@ -3775,7 +3771,7 @@
       <c r="F34" s="18">
         <v>124499.99999999999</v>
       </c>
-      <c r="G34" s="168">
+      <c r="G34" s="166">
         <f t="shared" ref="G34:G39" si="9">F34</f>
         <v>124499.99999999999</v>
       </c>
@@ -3794,7 +3790,7 @@
       <c r="K34" s="6"/>
       <c r="L34" s="33">
         <f t="shared" si="3"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="M34" s="33">
         <f t="shared" si="4"/>
@@ -3802,14 +3798,14 @@
       </c>
       <c r="N34" s="34">
         <f t="shared" si="5"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="O34" s="35">
         <f t="shared" si="6"/>
-        <v>126989.99999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>139233.65170302</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <f t="shared" si="8"/>
         <v>27</v>
@@ -3846,7 +3842,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="33">
         <f t="shared" si="3"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="M35" s="33">
         <f t="shared" si="4"/>
@@ -3854,15 +3850,15 @@
       </c>
       <c r="N35" s="34">
         <f t="shared" si="5"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="O35" s="35">
         <f t="shared" si="6"/>
-        <v>187170.00000000003</v>
+        <v>205215.86415666004</v>
       </c>
       <c r="P35" s="87"/>
     </row>
-    <row r="36" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <f t="shared" si="8"/>
         <v>28</v>
@@ -3882,7 +3878,7 @@
       <c r="F36" s="18">
         <v>139500</v>
       </c>
-      <c r="G36" s="168">
+      <c r="G36" s="166">
         <f t="shared" si="9"/>
         <v>139500</v>
       </c>
@@ -3901,7 +3897,7 @@
       <c r="K36" s="6"/>
       <c r="L36" s="33">
         <f t="shared" si="3"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="M36" s="33">
         <f t="shared" si="4"/>
@@ -3909,14 +3905,14 @@
       </c>
       <c r="N36" s="34">
         <f t="shared" si="5"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="O36" s="35">
         <f t="shared" si="6"/>
-        <v>142290</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>156008.79046242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <f t="shared" si="8"/>
         <v>29</v>
@@ -3928,25 +3924,24 @@
         <v>76</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E37" s="30">
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F37" s="18">
-        <v>124499.99999999999</v>
-      </c>
-      <c r="G37" s="168">
-        <f t="shared" si="9"/>
-        <v>124499.99999999999</v>
+        <v>126989.99999999999</v>
+      </c>
+      <c r="G37" s="166">
+        <v>124500</v>
       </c>
       <c r="H37" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2489.9999999999854</v>
       </c>
       <c r="I37" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>74.699999999999562</v>
       </c>
       <c r="J37" s="32">
         <f t="shared" si="2"/>
@@ -3955,7 +3950,7 @@
       <c r="K37" s="6"/>
       <c r="L37" s="33">
         <f t="shared" si="3"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="M37" s="33">
         <f t="shared" si="4"/>
@@ -3963,14 +3958,14 @@
       </c>
       <c r="N37" s="34">
         <f t="shared" si="5"/>
-        <v>124499.99999999999</v>
+        <v>139068.28010099998</v>
       </c>
       <c r="O37" s="35">
         <f t="shared" si="6"/>
-        <v>126989.99999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>141849.64570301998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <f t="shared" si="8"/>
         <v>30</v>
@@ -3982,17 +3977,17 @@
         <v>78</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E38" s="30">
         <v>2.1499999999999998E-2</v>
       </c>
       <c r="F38" s="18">
-        <v>351788.94167000049</v>
-      </c>
-      <c r="G38" s="168">
+        <v>107499.99999999999</v>
+      </c>
+      <c r="G38" s="166">
         <f t="shared" si="9"/>
-        <v>351788.94167000049</v>
+        <v>107499.99999999999</v>
       </c>
       <c r="H38" s="32">
         <f t="shared" si="0"/>
@@ -4009,7 +4004,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="33">
         <f t="shared" si="3"/>
-        <v>107499.99999999999</v>
+        <v>117864.537035</v>
       </c>
       <c r="M38" s="33">
         <f t="shared" si="4"/>
@@ -4017,14 +4012,14 @@
       </c>
       <c r="N38" s="34">
         <f t="shared" si="5"/>
-        <v>107499.99999999999</v>
+        <v>117864.537035</v>
       </c>
       <c r="O38" s="35">
         <f t="shared" si="6"/>
-        <v>109649.99999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>120221.8277757</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <f t="shared" si="8"/>
         <v>31</v>
@@ -4044,7 +4039,7 @@
       <c r="F39" s="18">
         <v>68000</v>
       </c>
-      <c r="G39" s="168">
+      <c r="G39" s="166">
         <f t="shared" si="9"/>
         <v>68000</v>
       </c>
@@ -4063,7 +4058,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="33">
         <f t="shared" si="3"/>
-        <v>68000</v>
+        <v>74556.172263999993</v>
       </c>
       <c r="M39" s="33">
         <f t="shared" si="4"/>
@@ -4071,14 +4066,14 @@
       </c>
       <c r="N39" s="34">
         <f t="shared" si="5"/>
-        <v>68000</v>
+        <v>74556.172263999993</v>
       </c>
       <c r="O39" s="35">
         <f t="shared" si="6"/>
-        <v>69360</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>76047.295709279992</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <f t="shared" si="8"/>
         <v>32</v>
@@ -4086,7 +4081,7 @@
       <c r="B40" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="170" t="s">
+      <c r="C40" s="228" t="s">
         <v>83</v>
       </c>
       <c r="D40" s="6"/>
@@ -4094,27 +4089,28 @@
         <v>2.7900000000000001E-2</v>
       </c>
       <c r="F40" s="18">
-        <v>142290</v>
-      </c>
-      <c r="G40" s="168">
-        <v>139500</v>
+        <v>142373.70000000001</v>
+      </c>
+      <c r="G40" s="166">
+        <f>2874+139500</f>
+        <v>142374</v>
       </c>
       <c r="H40" s="32">
         <f t="shared" si="0"/>
-        <v>2790</v>
+        <v>0</v>
       </c>
       <c r="I40" s="32">
         <f t="shared" si="1"/>
-        <v>83.7</v>
+        <v>0</v>
       </c>
       <c r="J40" s="32">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.29999999998835847</v>
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="33">
         <f t="shared" si="3"/>
-        <v>139500</v>
+        <v>152949.79457100001</v>
       </c>
       <c r="M40" s="33">
         <f t="shared" si="4"/>
@@ -4122,17 +4118,14 @@
       </c>
       <c r="N40" s="34">
         <f t="shared" si="5"/>
-        <v>142373.70000000001</v>
+        <v>152949.49457100002</v>
       </c>
       <c r="O40" s="35">
         <f t="shared" si="6"/>
-        <v>145221.174</v>
-      </c>
-      <c r="P40" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+        <v>156008.48446242002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <f t="shared" si="8"/>
         <v>33</v>
@@ -4144,25 +4137,24 @@
         <v>85</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E41" s="30">
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="F41" s="18">
-        <v>124499.99999999999</v>
-      </c>
-      <c r="G41" s="168">
-        <f>F41</f>
-        <v>124499.99999999999</v>
+        <v>126989.99999999999</v>
+      </c>
+      <c r="G41" s="166">
+        <v>124500</v>
       </c>
       <c r="H41" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2489.9999999999854</v>
       </c>
       <c r="I41" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>74.699999999999562</v>
       </c>
       <c r="J41" s="32">
         <f t="shared" si="2"/>
@@ -4171,7 +4163,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="33">
         <f t="shared" si="3"/>
-        <v>124499.99999999999</v>
+        <v>136503.580101</v>
       </c>
       <c r="M41" s="33">
         <f t="shared" si="4"/>
@@ -4179,14 +4171,14 @@
       </c>
       <c r="N41" s="34">
         <f t="shared" si="5"/>
-        <v>124499.99999999999</v>
+        <v>139068.28010099998</v>
       </c>
       <c r="O41" s="35">
         <f t="shared" si="6"/>
-        <v>126989.99999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>141849.64570301998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="57">
         <f t="shared" si="8"/>
         <v>34</v>
@@ -4204,19 +4196,18 @@
         <v>3.6700000000000003E-2</v>
       </c>
       <c r="F42" s="60">
-        <v>183500.00000000003</v>
-      </c>
-      <c r="G42" s="169">
-        <f>F42</f>
-        <v>183500.00000000003</v>
+        <v>187170.00000000003</v>
+      </c>
+      <c r="G42" s="167">
+        <v>183500</v>
       </c>
       <c r="H42" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3670.0000000000291</v>
       </c>
       <c r="I42" s="32">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>110.10000000000088</v>
       </c>
       <c r="J42" s="32">
         <f t="shared" si="2"/>
@@ -4225,7 +4216,7 @@
       <c r="K42" s="61"/>
       <c r="L42" s="33">
         <f t="shared" si="3"/>
-        <v>183500.00000000003</v>
+        <v>201192.02368300004</v>
       </c>
       <c r="M42" s="33">
         <f t="shared" si="4"/>
@@ -4233,14 +4224,14 @@
       </c>
       <c r="N42" s="34">
         <f t="shared" si="5"/>
-        <v>183500.00000000003</v>
+        <v>204972.12368300007</v>
       </c>
       <c r="O42" s="35">
         <f t="shared" si="6"/>
-        <v>187170.00000000003</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>209071.56615666006</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="62"/>
       <c r="B43" s="62"/>
       <c r="C43" s="63"/>
@@ -4251,23 +4242,23 @@
       </c>
       <c r="F43" s="65">
         <f>SUM(F9:F42)</f>
-        <v>6572422.9639698081</v>
+        <v>6270424.7326084664</v>
       </c>
       <c r="G43" s="143">
         <f t="shared" ref="G43:N43" si="10">SUM(G9:G42)</f>
-        <v>5380591.9416700006</v>
+        <v>4887946</v>
       </c>
       <c r="H43" s="66">
         <f t="shared" si="10"/>
-        <v>1195177.5837769071</v>
+        <v>1388661.5127288518</v>
       </c>
       <c r="I43" s="67">
         <f t="shared" si="10"/>
-        <v>35855.327513307209</v>
+        <v>41659.84538186554</v>
       </c>
       <c r="J43" s="68">
         <f t="shared" si="10"/>
-        <v>3346.5614770994143</v>
+        <v>6182.7801203865674</v>
       </c>
       <c r="K43" s="129">
         <f t="shared" si="10"/>
@@ -4275,7 +4266,7 @@
       </c>
       <c r="L43" s="65">
         <f t="shared" si="10"/>
-        <v>5017500</v>
+        <v>5501258.7402150016</v>
       </c>
       <c r="M43" s="65">
         <f t="shared" si="10"/>
@@ -4283,13 +4274,13 @@
       </c>
       <c r="N43" s="65">
         <f t="shared" si="10"/>
-        <v>6245186.3498131158</v>
+        <v>6925397.3182053324</v>
       </c>
       <c r="O43" s="65"/>
       <c r="P43" s="69"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="G45" s="166"/>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G45" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4305,21 +4296,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K110"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="24.5546875" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="8" max="8" width="25.44140625" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -4329,27 +4320,27 @@
       <c r="G1" s="72"/>
       <c r="H1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="38"/>
-      <c r="D2" s="217"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="219"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D2" s="181"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="183"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38"/>
       <c r="D3" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="220" t="s">
+      <c r="E3" s="184" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="220"/>
-      <c r="G3" s="220"/>
-      <c r="H3" s="221"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="185"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
       <c r="D4" s="74" t="s">
         <v>90</v>
@@ -4359,7 +4350,7 @@
       </c>
       <c r="H4" s="76"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="38"/>
       <c r="D5" s="74" t="s">
         <v>92</v>
@@ -4369,7 +4360,7 @@
       </c>
       <c r="H5" s="76"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="38"/>
       <c r="D6" s="74" t="s">
         <v>93</v>
@@ -4379,30 +4370,30 @@
       </c>
       <c r="H6" s="76"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="38"/>
       <c r="D7" s="74" t="s">
         <v>95</v>
       </c>
       <c r="H7" s="76"/>
     </row>
-    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="78" t="s">
         <v>96</v>
       </c>
       <c r="B8" s="79"/>
       <c r="C8" s="79" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="D8" s="79"/>
       <c r="E8" s="79"/>
       <c r="F8" s="80"/>
       <c r="G8" s="79" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="H8" s="81"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>97</v>
       </c>
@@ -4414,19 +4405,19 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="222" t="s">
+    <row r="10" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="186" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="223"/>
-      <c r="C10" s="223"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="223"/>
-      <c r="H10" s="224"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="187"/>
+      <c r="C10" s="187"/>
+      <c r="D10" s="187"/>
+      <c r="E10" s="187"/>
+      <c r="F10" s="187"/>
+      <c r="G10" s="187"/>
+      <c r="H10" s="188"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -4436,21 +4427,21 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="225" t="s">
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="189" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="225"/>
-      <c r="C12" s="225"/>
-      <c r="D12" s="225"/>
-      <c r="E12" s="225"/>
-      <c r="F12" s="225"/>
-      <c r="G12" s="225"/>
-      <c r="H12" s="225"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="189"/>
+      <c r="C12" s="189"/>
+      <c r="D12" s="189"/>
+      <c r="E12" s="189"/>
+      <c r="F12" s="189"/>
+      <c r="G12" s="189"/>
+      <c r="H12" s="189"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="150" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B13" s="151"/>
       <c r="C13" s="151"/>
@@ -4459,12 +4450,12 @@
       <c r="F13" s="151"/>
       <c r="G13" s="151"/>
       <c r="H13" s="82">
-        <v>1043827.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1057740.8999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="150" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B14" s="151"/>
       <c r="C14" s="151"/>
@@ -4473,10 +4464,10 @@
       <c r="F14" s="151"/>
       <c r="G14" s="151"/>
       <c r="H14" s="82">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="152" t="s">
         <v>101</v>
       </c>
@@ -4487,10 +4478,10 @@
       <c r="F15" s="152"/>
       <c r="G15" s="152"/>
       <c r="H15" s="82">
-        <v>-227032.41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-230058.66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="153" t="s">
         <v>100</v>
       </c>
@@ -4502,25 +4493,25 @@
       <c r="G16" s="154"/>
       <c r="H16" s="84">
         <f>SUM(H13:H15)</f>
-        <v>816794.99999999988</v>
+        <v>827682.99999999988</v>
       </c>
       <c r="I16" s="83"/>
     </row>
-    <row r="17" spans="1:9" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="226" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" s="226"/>
-      <c r="C17" s="226"/>
-      <c r="D17" s="226"/>
-      <c r="E17" s="226"/>
-      <c r="F17" s="226"/>
-      <c r="G17" s="226"/>
-      <c r="H17" s="226"/>
-    </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="190" t="s">
+        <v>160</v>
+      </c>
+      <c r="B17" s="190"/>
+      <c r="C17" s="190"/>
+      <c r="D17" s="190"/>
+      <c r="E17" s="190"/>
+      <c r="F17" s="190"/>
+      <c r="G17" s="190"/>
+      <c r="H17" s="190"/>
+    </row>
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="85" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B18" s="151"/>
       <c r="C18" s="151"/>
@@ -4530,9 +4521,9 @@
       <c r="G18" s="151"/>
       <c r="H18" s="82"/>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="85" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B19" s="151"/>
       <c r="C19" s="151"/>
@@ -4542,7 +4533,7 @@
       <c r="G19" s="151"/>
       <c r="H19" s="82"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="151"/>
       <c r="B20" s="151"/>
       <c r="C20" s="151"/>
@@ -4552,7 +4543,7 @@
       <c r="G20" s="151"/>
       <c r="H20" s="82"/>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="151" t="s">
         <v>102</v>
       </c>
@@ -4567,41 +4558,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="226" t="s">
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="190" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="226"/>
-      <c r="C22" s="226"/>
-      <c r="D22" s="226"/>
-      <c r="E22" s="226"/>
-      <c r="F22" s="226"/>
-      <c r="G22" s="226"/>
-      <c r="H22" s="226"/>
-    </row>
-    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="190"/>
+      <c r="C22" s="190"/>
+      <c r="D22" s="190"/>
+      <c r="E22" s="190"/>
+      <c r="F22" s="190"/>
+      <c r="G22" s="190"/>
+      <c r="H22" s="190"/>
+    </row>
+    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="150" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="155" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C23" s="155"/>
       <c r="D23" s="155"/>
       <c r="E23" s="155"/>
       <c r="F23" s="155"/>
       <c r="G23" s="151"/>
-      <c r="H23" s="231">
+      <c r="H23" s="82">
         <v>92476.76</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="150" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B24" s="151" t="str">
         <f>B23</f>
-        <v>Debito 14/07</v>
+        <v>Debito 13/08</v>
       </c>
       <c r="C24" s="155"/>
       <c r="D24" s="155"/>
@@ -4609,43 +4600,44 @@
       <c r="F24" s="155"/>
       <c r="G24" s="151"/>
       <c r="H24" s="82">
-        <v>69862.55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>46972.22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="150" t="s">
         <v>105</v>
       </c>
       <c r="B25" s="151" t="str">
         <f>B24</f>
-        <v>Debito 14/07</v>
+        <v>Debito 13/08</v>
       </c>
       <c r="C25" s="155"/>
       <c r="D25" s="155"/>
       <c r="E25" s="155"/>
       <c r="F25" s="155"/>
       <c r="G25" s="151"/>
-      <c r="H25" s="231">
+      <c r="H25" s="82">
         <v>5219.1400000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="150" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B26" s="151" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C26" s="155"/>
       <c r="D26" s="155"/>
       <c r="E26" s="155"/>
       <c r="F26" s="155"/>
       <c r="G26" s="151"/>
-      <c r="H26" s="231">
-        <v>480315.88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H26" s="82">
+        <f>61422.03+480315.88</f>
+        <v>541737.91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="150"/>
       <c r="B27" s="151"/>
       <c r="C27" s="155"/>
@@ -4657,7 +4649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="154" t="s">
         <v>106</v>
       </c>
@@ -4669,22 +4661,22 @@
       <c r="G28" s="154"/>
       <c r="H28" s="84">
         <f>SUM(H23:H27)</f>
-        <v>647874.33000000007</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="216" t="s">
+        <v>686406.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="180" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="216"/>
-      <c r="C29" s="216"/>
-      <c r="D29" s="216"/>
-      <c r="E29" s="216"/>
-      <c r="F29" s="216"/>
-      <c r="G29" s="216"/>
-      <c r="H29" s="216"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="180"/>
+      <c r="C29" s="180"/>
+      <c r="D29" s="180"/>
+      <c r="E29" s="180"/>
+      <c r="F29" s="180"/>
+      <c r="G29" s="180"/>
+      <c r="H29" s="180"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="151" t="s">
         <v>108</v>
       </c>
@@ -4692,15 +4684,15 @@
       <c r="C30" s="151"/>
       <c r="D30" s="151"/>
       <c r="E30" s="151" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="F30" s="151"/>
       <c r="G30" s="151"/>
-      <c r="H30" s="231">
-        <v>4404.8100000000004</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H30" s="82">
+        <v>4381.32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="151" t="s">
         <v>109</v>
       </c>
@@ -4710,16 +4702,16 @@
       <c r="C31" s="151"/>
       <c r="D31" s="151"/>
       <c r="E31" s="151" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F31" s="151"/>
       <c r="G31" s="151"/>
-      <c r="H31" s="231">
+      <c r="H31" s="82">
         <v>1073579.78</v>
       </c>
       <c r="I31" s="87"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="156" t="s">
         <v>111</v>
       </c>
@@ -4731,11 +4723,11 @@
       <c r="E32" s="151"/>
       <c r="F32" s="151"/>
       <c r="G32" s="151"/>
-      <c r="H32" s="231">
-        <v>197929.65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H32" s="82">
+        <v>196434.48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="154" t="s">
         <v>100</v>
       </c>
@@ -4747,370 +4739,369 @@
       <c r="G33" s="154"/>
       <c r="H33" s="157">
         <f>SUM(H30:H32)</f>
-        <v>1275914.24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="216" t="s">
+        <v>1274395.58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="180" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="216"/>
-      <c r="C34" s="216"/>
-      <c r="D34" s="216"/>
-      <c r="E34" s="216"/>
-      <c r="F34" s="216"/>
-      <c r="G34" s="216"/>
-      <c r="H34" s="216"/>
-    </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="85"/>
+      <c r="B34" s="180"/>
+      <c r="C34" s="180"/>
+      <c r="D34" s="180"/>
+      <c r="E34" s="180"/>
+      <c r="F34" s="180"/>
+      <c r="G34" s="180"/>
+      <c r="H34" s="180"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="85" t="s">
+        <v>156</v>
+      </c>
       <c r="B35" s="158"/>
       <c r="C35" s="151"/>
       <c r="D35" s="151"/>
       <c r="E35" s="151"/>
       <c r="F35" s="151"/>
       <c r="G35" s="151"/>
-      <c r="H35" s="82"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H35" s="82">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="85" t="s">
-        <v>158</v>
-      </c>
-      <c r="B36" s="158"/>
-      <c r="C36" s="151"/>
-      <c r="D36" s="151"/>
-      <c r="E36" s="151"/>
-      <c r="F36" s="151"/>
-      <c r="G36" s="151"/>
-      <c r="H36" s="231">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="85" t="s">
-        <v>181</v>
-      </c>
-      <c r="B37" s="159"/>
-      <c r="C37" s="85"/>
-      <c r="D37" s="85"/>
-      <c r="E37" s="85"/>
-      <c r="F37" s="85"/>
-      <c r="G37" s="85"/>
-      <c r="H37" s="231">
+        <v>174</v>
+      </c>
+      <c r="B36" s="159"/>
+      <c r="C36" s="85"/>
+      <c r="D36" s="85"/>
+      <c r="E36" s="85"/>
+      <c r="F36" s="85"/>
+      <c r="G36" s="85"/>
+      <c r="H36" s="82">
         <v>45000</v>
       </c>
-      <c r="J37" s="87"/>
-    </row>
-    <row r="38" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="194" t="s">
-        <v>179</v>
-      </c>
-      <c r="B38" s="195"/>
-      <c r="C38" s="195"/>
-      <c r="D38" s="195"/>
-      <c r="E38" s="195"/>
-      <c r="F38" s="195"/>
-      <c r="G38" s="196"/>
-      <c r="H38" s="231">
+      <c r="J36" s="87"/>
+    </row>
+    <row r="37" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="197" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" s="198"/>
+      <c r="C37" s="198"/>
+      <c r="D37" s="198"/>
+      <c r="E37" s="198"/>
+      <c r="F37" s="198"/>
+      <c r="G37" s="199"/>
+      <c r="H37" s="82">
         <v>24100</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="194" t="s">
-        <v>180</v>
-      </c>
-      <c r="B39" s="195"/>
-      <c r="C39" s="195"/>
-      <c r="D39" s="195"/>
-      <c r="E39" s="195"/>
-      <c r="F39" s="195"/>
-      <c r="G39" s="196"/>
-      <c r="H39" s="231">
+    <row r="38" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="197" t="s">
+        <v>177</v>
+      </c>
+      <c r="B38" s="198"/>
+      <c r="C38" s="198"/>
+      <c r="D38" s="198"/>
+      <c r="E38" s="198"/>
+      <c r="F38" s="198"/>
+      <c r="G38" s="199"/>
+      <c r="H38" s="82">
         <v>24100</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="85" t="s">
-        <v>178</v>
-      </c>
-      <c r="B40" s="158"/>
-      <c r="C40" s="151"/>
-      <c r="D40" s="151"/>
-      <c r="E40" s="151"/>
-      <c r="F40" s="151"/>
-      <c r="G40" s="151"/>
-      <c r="H40" s="231">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="85" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" s="158"/>
+      <c r="C39" s="151"/>
+      <c r="D39" s="151"/>
+      <c r="E39" s="151"/>
+      <c r="F39" s="151"/>
+      <c r="G39" s="151"/>
+      <c r="H39" s="82">
         <v>112550</v>
       </c>
-      <c r="I40" s="148"/>
-      <c r="J40" s="181"/>
-    </row>
-    <row r="41" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="194" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" s="195"/>
-      <c r="C41" s="195"/>
-      <c r="D41" s="195"/>
-      <c r="E41" s="195"/>
-      <c r="F41" s="195"/>
-      <c r="G41" s="196"/>
-      <c r="H41" s="231">
+      <c r="I39" s="148"/>
+      <c r="J39" s="200"/>
+    </row>
+    <row r="40" spans="1:10" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="197" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" s="198"/>
+      <c r="C40" s="198"/>
+      <c r="D40" s="198"/>
+      <c r="E40" s="198"/>
+      <c r="F40" s="198"/>
+      <c r="G40" s="199"/>
+      <c r="H40" s="82">
         <v>741000</v>
       </c>
-      <c r="J41" s="181"/>
-    </row>
-    <row r="42" spans="1:10" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="96" t="s">
-        <v>166</v>
-      </c>
-      <c r="B42" s="164"/>
-      <c r="C42" s="164"/>
-      <c r="D42" s="164"/>
-      <c r="E42" s="164"/>
-      <c r="F42" s="164"/>
-      <c r="G42" s="165"/>
-      <c r="H42" s="82">
-        <v>36300</v>
-      </c>
-      <c r="J42" s="181"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J40" s="200"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="151" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="151"/>
+      <c r="C41" s="151"/>
+      <c r="D41" s="151"/>
+      <c r="E41" s="151"/>
+      <c r="F41" s="151"/>
+      <c r="G41" s="151"/>
+      <c r="H41" s="84">
+        <f>SUM(H35:H40)</f>
+        <v>1086750</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="180" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="180"/>
+      <c r="C42" s="180"/>
+      <c r="D42" s="180"/>
+      <c r="E42" s="180"/>
+      <c r="F42" s="180"/>
+      <c r="G42" s="180"/>
+      <c r="H42" s="180"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="151" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B43" s="151"/>
-      <c r="C43" s="151"/>
-      <c r="D43" s="151"/>
+      <c r="C43" s="151" t="s">
+        <v>167</v>
+      </c>
+      <c r="D43" s="160"/>
       <c r="E43" s="151"/>
       <c r="F43" s="151"/>
       <c r="G43" s="151"/>
-      <c r="H43" s="84">
-        <f>SUM(H35:H42)</f>
-        <v>1123050</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="216" t="s">
-        <v>114</v>
-      </c>
-      <c r="B44" s="216"/>
-      <c r="C44" s="216"/>
-      <c r="D44" s="216"/>
-      <c r="E44" s="216"/>
-      <c r="F44" s="216"/>
-      <c r="G44" s="216"/>
-      <c r="H44" s="216"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H43" s="82">
+        <v>265000</v>
+      </c>
+      <c r="J43" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="161" t="s">
+        <v>145</v>
+      </c>
+      <c r="B44" s="151"/>
+      <c r="C44" s="218"/>
+      <c r="D44" s="219"/>
+      <c r="E44" s="162"/>
+      <c r="F44" s="155"/>
+      <c r="G44" s="151"/>
+      <c r="H44" s="82">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="151" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="B45" s="151"/>
-      <c r="C45" s="151" t="s">
-        <v>176</v>
-      </c>
-      <c r="D45" s="160"/>
-      <c r="E45" s="151"/>
-      <c r="F45" s="151"/>
+      <c r="C45" s="155"/>
+      <c r="D45" s="155"/>
+      <c r="E45" s="155"/>
+      <c r="F45" s="155"/>
       <c r="G45" s="151"/>
       <c r="H45" s="82">
-        <v>265000</v>
-      </c>
-      <c r="J45" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="161" t="s">
-        <v>147</v>
-      </c>
-      <c r="B46" s="151"/>
-      <c r="C46" s="202"/>
-      <c r="D46" s="203"/>
-      <c r="E46" s="162"/>
-      <c r="F46" s="155"/>
-      <c r="G46" s="151"/>
-      <c r="H46" s="231">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="151"/>
-      <c r="B47" s="151"/>
-      <c r="C47" s="155"/>
-      <c r="D47" s="155"/>
-      <c r="E47" s="155"/>
-      <c r="F47" s="155"/>
-      <c r="G47" s="151"/>
-      <c r="H47" s="82"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="154" t="s">
+        <v>195000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="154" t="s">
         <v>100</v>
       </c>
-      <c r="B48" s="154"/>
-      <c r="C48" s="154"/>
-      <c r="D48" s="154"/>
-      <c r="E48" s="154"/>
-      <c r="F48" s="154"/>
-      <c r="G48" s="154"/>
-      <c r="H48" s="84">
-        <f>SUM(H45:H47)</f>
-        <v>295000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="227" t="s">
+      <c r="B46" s="154"/>
+      <c r="C46" s="154"/>
+      <c r="D46" s="154"/>
+      <c r="E46" s="154"/>
+      <c r="F46" s="154"/>
+      <c r="G46" s="154"/>
+      <c r="H46" s="84">
+        <f>SUM(H43:H45)</f>
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="191" t="s">
         <v>116</v>
       </c>
-      <c r="B49" s="228"/>
-      <c r="C49" s="228"/>
-      <c r="D49" s="228"/>
-      <c r="E49" s="228"/>
-      <c r="F49" s="228"/>
-      <c r="G49" s="228"/>
-      <c r="H49" s="229"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="151" t="s">
+      <c r="B47" s="192"/>
+      <c r="C47" s="192"/>
+      <c r="D47" s="192"/>
+      <c r="E47" s="192"/>
+      <c r="F47" s="192"/>
+      <c r="G47" s="192"/>
+      <c r="H47" s="193"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="151" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="151"/>
-      <c r="C50" s="151"/>
-      <c r="D50" s="151"/>
-      <c r="E50" s="151"/>
-      <c r="F50" s="151"/>
-      <c r="G50" s="151"/>
-      <c r="H50" s="82">
-        <v>60887.77</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="151"/>
-      <c r="B51" s="151"/>
-      <c r="C51" s="151"/>
-      <c r="D51" s="151"/>
-      <c r="E51" s="151"/>
-      <c r="F51" s="151"/>
-      <c r="G51" s="151"/>
-      <c r="H51" s="82"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="154" t="s">
+      <c r="B48" s="151"/>
+      <c r="C48" s="151"/>
+      <c r="D48" s="151"/>
+      <c r="E48" s="151"/>
+      <c r="F48" s="151"/>
+      <c r="G48" s="151"/>
+      <c r="H48" s="82">
+        <v>58309.62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="151"/>
+      <c r="B49" s="151"/>
+      <c r="C49" s="151"/>
+      <c r="D49" s="151"/>
+      <c r="E49" s="151"/>
+      <c r="F49" s="151"/>
+      <c r="G49" s="151"/>
+      <c r="H49" s="82"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="154" t="s">
         <v>106</v>
       </c>
-      <c r="B52" s="154"/>
-      <c r="C52" s="154"/>
-      <c r="D52" s="154"/>
-      <c r="E52" s="154"/>
-      <c r="F52" s="154"/>
-      <c r="G52" s="154"/>
-      <c r="H52" s="157">
-        <f>SUM(H50:H51)</f>
-        <v>60887.77</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="227" t="s">
+      <c r="B50" s="154"/>
+      <c r="C50" s="154"/>
+      <c r="D50" s="154"/>
+      <c r="E50" s="154"/>
+      <c r="F50" s="154"/>
+      <c r="G50" s="154"/>
+      <c r="H50" s="157">
+        <f>SUM(H48:H49)</f>
+        <v>58309.62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="191" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="228"/>
-      <c r="C53" s="228"/>
-      <c r="D53" s="228"/>
-      <c r="E53" s="228"/>
-      <c r="F53" s="228"/>
-      <c r="G53" s="228"/>
-      <c r="H53" s="229"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="192"/>
+      <c r="D51" s="192"/>
+      <c r="E51" s="192"/>
+      <c r="F51" s="192"/>
+      <c r="G51" s="192"/>
+      <c r="H51" s="193"/>
+      <c r="I51" s="87"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" s="85"/>
+      <c r="C52" s="85"/>
+      <c r="D52" s="85"/>
+      <c r="E52" s="85"/>
+      <c r="F52" s="85" t="s">
+        <v>178</v>
+      </c>
+      <c r="G52" s="85"/>
+      <c r="H52" s="82">
+        <v>55029.24</v>
+      </c>
+      <c r="I52" s="87"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="85" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="85"/>
+      <c r="C53" s="85"/>
+      <c r="D53" s="85"/>
+      <c r="E53" s="85"/>
+      <c r="F53" s="85" t="s">
+        <v>172</v>
+      </c>
+      <c r="G53" s="85"/>
+      <c r="H53" s="82">
+        <v>3498.02</v>
+      </c>
       <c r="I53" s="87"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="85" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="B54" s="85"/>
       <c r="C54" s="85"/>
       <c r="D54" s="85"/>
       <c r="E54" s="85"/>
-      <c r="F54" s="85" t="s">
-        <v>171</v>
-      </c>
+      <c r="F54" s="85"/>
       <c r="G54" s="85"/>
-      <c r="H54" s="82">
-        <v>55029.24</v>
+      <c r="H54" s="84">
+        <f>SUM(H52:H53)</f>
+        <v>58527.259999999995</v>
       </c>
       <c r="I54" s="87"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="B55" s="85"/>
-      <c r="C55" s="85"/>
-      <c r="D55" s="85"/>
-      <c r="E55" s="85"/>
-      <c r="F55" s="85" t="s">
-        <v>170</v>
-      </c>
-      <c r="G55" s="85"/>
-      <c r="H55" s="82">
-        <v>3498.02</v>
-      </c>
-      <c r="I55" s="87"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="85" t="s">
+      <c r="K54" s="83"/>
+    </row>
+    <row r="55" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="195"/>
+      <c r="C55" s="195"/>
+      <c r="D55" s="195"/>
+      <c r="E55" s="195"/>
+      <c r="F55" s="195"/>
+      <c r="G55" s="195"/>
+      <c r="H55" s="196"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="86"/>
+      <c r="B56" s="86"/>
+      <c r="C56" s="86"/>
+      <c r="D56" s="86"/>
+      <c r="E56" s="86"/>
+      <c r="F56" s="86"/>
+      <c r="G56" s="86"/>
+      <c r="H56" s="90"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="86"/>
+      <c r="B57" s="86"/>
+      <c r="C57" s="86"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="86"/>
+      <c r="F57" s="86"/>
+      <c r="G57" s="86"/>
+      <c r="H57" s="90"/>
+    </row>
+    <row r="58" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="B56" s="85"/>
-      <c r="C56" s="85"/>
-      <c r="D56" s="85"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="85"/>
-      <c r="G56" s="85"/>
-      <c r="H56" s="84">
-        <f>SUM(H54:H55)</f>
-        <v>58527.259999999995</v>
-      </c>
-      <c r="I56" s="87"/>
-      <c r="K56" s="83"/>
-    </row>
-    <row r="57" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="204" t="s">
-        <v>119</v>
-      </c>
-      <c r="B57" s="205"/>
-      <c r="C57" s="205"/>
-      <c r="D57" s="205"/>
-      <c r="E57" s="205"/>
-      <c r="F57" s="205"/>
-      <c r="G57" s="205"/>
-      <c r="H57" s="230"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="86"/>
-      <c r="B58" s="86"/>
-      <c r="C58" s="86"/>
-      <c r="D58" s="86"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="86"/>
-      <c r="G58" s="86"/>
-      <c r="H58" s="90"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="86"/>
-      <c r="B59" s="86"/>
-      <c r="C59" s="86"/>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
-      <c r="H59" s="90"/>
-    </row>
-    <row r="60" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="A60" s="91" t="s">
-        <v>100</v>
-      </c>
+      <c r="B58" s="89"/>
+      <c r="C58" s="89"/>
+      <c r="D58" s="89"/>
+      <c r="E58" s="89"/>
+      <c r="F58" s="89"/>
+      <c r="G58" s="89"/>
+      <c r="H58" s="92"/>
+    </row>
+    <row r="59" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="93"/>
+      <c r="B59" s="131"/>
+      <c r="C59" s="131"/>
+      <c r="D59" s="131"/>
+      <c r="E59" s="131"/>
+      <c r="F59" s="131"/>
+      <c r="G59" s="131"/>
+      <c r="H59" s="94"/>
+    </row>
+    <row r="60" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="91"/>
       <c r="B60" s="89"/>
       <c r="C60" s="89"/>
       <c r="D60" s="89"/>
@@ -5119,17 +5110,19 @@
       <c r="G60" s="89"/>
       <c r="H60" s="92"/>
     </row>
-    <row r="61" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="A61" s="93"/>
-      <c r="B61" s="131"/>
-      <c r="C61" s="131"/>
-      <c r="D61" s="131"/>
-      <c r="E61" s="131"/>
-      <c r="F61" s="131"/>
-      <c r="G61" s="131"/>
-      <c r="H61" s="94"/>
-    </row>
-    <row r="62" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="194" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" s="195"/>
+      <c r="C61" s="195"/>
+      <c r="D61" s="195"/>
+      <c r="E61" s="195"/>
+      <c r="F61" s="195"/>
+      <c r="G61" s="195"/>
+      <c r="H61" s="127"/>
+    </row>
+    <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="91"/>
       <c r="B62" s="89"/>
       <c r="C62" s="89"/>
@@ -5139,29 +5132,32 @@
       <c r="G62" s="89"/>
       <c r="H62" s="92"/>
     </row>
-    <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="204" t="s">
-        <v>152</v>
-      </c>
-      <c r="B63" s="205"/>
-      <c r="C63" s="205"/>
-      <c r="D63" s="205"/>
-      <c r="E63" s="205"/>
-      <c r="F63" s="205"/>
-      <c r="G63" s="205"/>
-      <c r="H63" s="127"/>
-    </row>
-    <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="91"/>
-      <c r="B64" s="89"/>
-      <c r="C64" s="89"/>
-      <c r="D64" s="89"/>
-      <c r="E64" s="89"/>
-      <c r="F64" s="89"/>
-      <c r="G64" s="89"/>
-      <c r="H64" s="92"/>
-    </row>
-    <row r="65" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="91"/>
+      <c r="B63" s="89"/>
+      <c r="C63" s="89"/>
+      <c r="D63" s="89"/>
+      <c r="E63" s="89"/>
+      <c r="F63" s="89"/>
+      <c r="G63" s="89"/>
+      <c r="H63" s="92"/>
+    </row>
+    <row r="64" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="128" t="s">
+        <v>100</v>
+      </c>
+      <c r="B64" s="131"/>
+      <c r="C64" s="131"/>
+      <c r="D64" s="131"/>
+      <c r="E64" s="131"/>
+      <c r="F64" s="131"/>
+      <c r="G64" s="131"/>
+      <c r="H64" s="94">
+        <f>SUM(H62:H63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A65" s="91"/>
       <c r="B65" s="89"/>
       <c r="C65" s="89"/>
@@ -5171,317 +5167,321 @@
       <c r="G65" s="89"/>
       <c r="H65" s="92"/>
     </row>
-    <row r="66" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="128" t="s">
+    <row r="66" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A66" s="212" t="s">
+        <v>120</v>
+      </c>
+      <c r="B66" s="212"/>
+      <c r="C66" s="212"/>
+      <c r="D66" s="212"/>
+      <c r="E66" s="212"/>
+      <c r="F66" s="212"/>
+      <c r="G66" s="212"/>
+      <c r="H66" s="95"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="197"/>
+      <c r="B67" s="198"/>
+      <c r="C67" s="198"/>
+      <c r="D67" s="198"/>
+      <c r="E67" s="198"/>
+      <c r="F67" s="198"/>
+      <c r="G67" s="199"/>
+      <c r="H67" s="123"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="96"/>
+      <c r="B68" s="97"/>
+      <c r="C68" s="97"/>
+      <c r="D68" s="97"/>
+      <c r="E68" s="97"/>
+      <c r="F68" s="97"/>
+      <c r="G68" s="98"/>
+      <c r="H68" s="123"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="213"/>
+      <c r="B69" s="214"/>
+      <c r="C69" s="214"/>
+      <c r="D69" s="214"/>
+      <c r="E69" s="214"/>
+      <c r="F69" s="214"/>
+      <c r="G69" s="215"/>
+      <c r="H69" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="132"/>
+      <c r="B70" s="133"/>
+      <c r="C70" s="133"/>
+      <c r="D70" s="133"/>
+      <c r="E70" s="133"/>
+      <c r="F70" s="133"/>
+      <c r="G70" s="134"/>
+      <c r="H70" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="132"/>
+      <c r="B71" s="133"/>
+      <c r="C71" s="133"/>
+      <c r="D71" s="133"/>
+      <c r="E71" s="133"/>
+      <c r="F71" s="133"/>
+      <c r="G71" s="134"/>
+      <c r="H71" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="136" t="s">
         <v>100</v>
       </c>
-      <c r="B66" s="131"/>
-      <c r="C66" s="131"/>
-      <c r="D66" s="131"/>
-      <c r="E66" s="131"/>
-      <c r="F66" s="131"/>
-      <c r="G66" s="131"/>
-      <c r="H66" s="94">
-        <f>SUM(H64:H65)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="A67" s="91"/>
-      <c r="B67" s="89"/>
-      <c r="C67" s="89"/>
-      <c r="D67" s="89"/>
-      <c r="E67" s="89"/>
-      <c r="F67" s="89"/>
-      <c r="G67" s="89"/>
-      <c r="H67" s="92"/>
-    </row>
-    <row r="68" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A68" s="193" t="s">
-        <v>120</v>
-      </c>
-      <c r="B68" s="193"/>
-      <c r="C68" s="193"/>
-      <c r="D68" s="193"/>
-      <c r="E68" s="193"/>
-      <c r="F68" s="193"/>
-      <c r="G68" s="193"/>
-      <c r="H68" s="95"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="194"/>
-      <c r="B69" s="195"/>
-      <c r="C69" s="195"/>
-      <c r="D69" s="195"/>
-      <c r="E69" s="195"/>
-      <c r="F69" s="195"/>
-      <c r="G69" s="196"/>
-      <c r="H69" s="123"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="96"/>
-      <c r="B70" s="97"/>
-      <c r="C70" s="97"/>
-      <c r="D70" s="97"/>
-      <c r="E70" s="97"/>
-      <c r="F70" s="97"/>
-      <c r="G70" s="98"/>
-      <c r="H70" s="123"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="197"/>
-      <c r="B71" s="198"/>
-      <c r="C71" s="198"/>
-      <c r="D71" s="198"/>
-      <c r="E71" s="198"/>
-      <c r="F71" s="198"/>
-      <c r="G71" s="199"/>
-      <c r="H71" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="132"/>
-      <c r="B72" s="133"/>
-      <c r="C72" s="133"/>
-      <c r="D72" s="133"/>
-      <c r="E72" s="133"/>
-      <c r="F72" s="133"/>
-      <c r="G72" s="134"/>
-      <c r="H72" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="132"/>
-      <c r="B73" s="133"/>
-      <c r="C73" s="133"/>
-      <c r="D73" s="133"/>
-      <c r="E73" s="133"/>
-      <c r="F73" s="133"/>
-      <c r="G73" s="134"/>
-      <c r="H73" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="136" t="s">
-        <v>100</v>
-      </c>
-      <c r="B74" s="85"/>
-      <c r="C74" s="85"/>
-      <c r="D74" s="85"/>
-      <c r="E74" s="85"/>
-      <c r="F74" s="85"/>
-      <c r="G74" s="85"/>
-      <c r="H74" s="84">
-        <f>SUM(H69:H73)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="137"/>
-      <c r="B75" s="137"/>
-      <c r="C75" s="137"/>
-      <c r="D75" s="137"/>
-      <c r="E75" s="137"/>
-      <c r="F75" s="137"/>
-      <c r="G75" s="137"/>
-      <c r="H75" s="138"/>
-      <c r="I75" s="87"/>
-    </row>
-    <row r="76" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="200" t="s">
+      <c r="B72" s="85"/>
+      <c r="C72" s="85"/>
+      <c r="D72" s="85"/>
+      <c r="E72" s="85"/>
+      <c r="F72" s="85"/>
+      <c r="G72" s="85"/>
+      <c r="H72" s="84">
+        <f>SUM(H67:H71)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="137"/>
+      <c r="B73" s="137"/>
+      <c r="C73" s="137"/>
+      <c r="D73" s="137"/>
+      <c r="E73" s="137"/>
+      <c r="F73" s="137"/>
+      <c r="G73" s="137"/>
+      <c r="H73" s="138"/>
+      <c r="I73" s="87"/>
+    </row>
+    <row r="74" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="216" t="s">
         <v>121</v>
       </c>
-      <c r="B76" s="201"/>
-      <c r="C76" s="201"/>
-      <c r="D76" s="201"/>
-      <c r="E76" s="201"/>
-      <c r="F76" s="201"/>
-      <c r="G76" s="201"/>
-      <c r="H76" s="139">
-        <f>H74</f>
-        <v>0</v>
-      </c>
+      <c r="B74" s="217"/>
+      <c r="C74" s="217"/>
+      <c r="D74" s="217"/>
+      <c r="E74" s="217"/>
+      <c r="F74" s="217"/>
+      <c r="G74" s="217"/>
+      <c r="H74" s="139">
+        <f>H72</f>
+        <v>0</v>
+      </c>
+      <c r="I74" s="87"/>
+    </row>
+    <row r="75" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="209" t="s">
+        <v>182</v>
+      </c>
+      <c r="B75" s="210"/>
+      <c r="C75" s="210"/>
+      <c r="D75" s="210"/>
+      <c r="E75" s="210"/>
+      <c r="F75" s="210"/>
+      <c r="G75" s="211"/>
+      <c r="H75" s="139">
+        <v>1000000</v>
+      </c>
+      <c r="I75" s="88"/>
+    </row>
+    <row r="76" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="220" t="s">
+        <v>140</v>
+      </c>
+      <c r="B76" s="221"/>
+      <c r="C76" s="221"/>
+      <c r="D76" s="221"/>
+      <c r="E76" s="221"/>
+      <c r="F76" s="221"/>
+      <c r="G76" s="222"/>
+      <c r="H76" s="139"/>
       <c r="I76" s="87"/>
-    </row>
-    <row r="77" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="190" t="s">
+      <c r="J76" s="83"/>
+    </row>
+    <row r="77" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A77" s="216" t="s">
         <v>122</v>
       </c>
-      <c r="B77" s="191"/>
-      <c r="C77" s="191"/>
-      <c r="D77" s="191"/>
-      <c r="E77" s="191"/>
-      <c r="F77" s="191"/>
-      <c r="G77" s="192"/>
+      <c r="B77" s="217"/>
+      <c r="C77" s="217"/>
+      <c r="D77" s="217"/>
+      <c r="E77" s="217"/>
+      <c r="F77" s="217"/>
+      <c r="G77" s="217"/>
       <c r="H77" s="139">
-        <f>J80-4553581.78+20000</f>
-        <v>466418.21999999974</v>
-      </c>
-      <c r="I77" s="88"/>
-    </row>
-    <row r="78" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="206" t="s">
-        <v>142</v>
-      </c>
-      <c r="B78" s="207"/>
-      <c r="C78" s="207"/>
-      <c r="D78" s="207"/>
-      <c r="E78" s="207"/>
-      <c r="F78" s="207"/>
-      <c r="G78" s="208"/>
-      <c r="H78" s="139"/>
-      <c r="I78" s="87"/>
-      <c r="J78" s="83"/>
-    </row>
-    <row r="79" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A79" s="200" t="s">
+        <f>H58+H54+H50+H46+H41+H33+H16+H21+H28+H64</f>
+        <v>4482071.49</v>
+      </c>
+      <c r="I77" s="83"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A78" s="223" t="s">
         <v>123</v>
       </c>
-      <c r="B79" s="201"/>
-      <c r="C79" s="201"/>
-      <c r="D79" s="201"/>
-      <c r="E79" s="201"/>
-      <c r="F79" s="201"/>
-      <c r="G79" s="201"/>
-      <c r="H79" s="139">
-        <f>H60+H56+H52+H48+H43+H33+H16+H21+H28+H66</f>
-        <v>4278048.5999999996</v>
+      <c r="B78" s="224"/>
+      <c r="C78" s="224"/>
+      <c r="D78" s="224"/>
+      <c r="E78" s="224"/>
+      <c r="F78" s="224"/>
+      <c r="G78" s="225"/>
+      <c r="H78" s="140">
+        <f>H77+H75</f>
+        <v>5482071.4900000002</v>
+      </c>
+      <c r="I78" s="83"/>
+      <c r="J78">
+        <v>5000000</v>
+      </c>
+      <c r="K78" s="148"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A79" s="223" t="s">
+        <v>124</v>
+      </c>
+      <c r="B79" s="224"/>
+      <c r="C79" s="224"/>
+      <c r="D79" s="224"/>
+      <c r="E79" s="224"/>
+      <c r="F79" s="224"/>
+      <c r="G79" s="225"/>
+      <c r="H79" s="141">
+        <f>H74+H76</f>
+        <v>0</v>
       </c>
       <c r="I79" s="83"/>
-    </row>
-    <row r="80" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A80" s="209" t="s">
-        <v>124</v>
-      </c>
-      <c r="B80" s="210"/>
-      <c r="C80" s="210"/>
-      <c r="D80" s="210"/>
-      <c r="E80" s="210"/>
-      <c r="F80" s="210"/>
-      <c r="G80" s="211"/>
-      <c r="H80" s="140">
-        <f>H79+H77</f>
-        <v>4744466.8199999994</v>
-      </c>
-      <c r="I80" s="83"/>
-      <c r="J80">
-        <v>5000000</v>
-      </c>
-      <c r="K80" s="148"/>
-    </row>
-    <row r="81" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A81" s="209" t="s">
+      <c r="J79" s="148"/>
+    </row>
+    <row r="80" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="226" t="s">
         <v>125</v>
       </c>
-      <c r="B81" s="210"/>
-      <c r="C81" s="210"/>
-      <c r="D81" s="210"/>
-      <c r="E81" s="210"/>
-      <c r="F81" s="210"/>
-      <c r="G81" s="211"/>
-      <c r="H81" s="141">
-        <f>H76+H78</f>
-        <v>0</v>
-      </c>
-      <c r="I81" s="83"/>
-      <c r="J81" s="148"/>
-    </row>
-    <row r="82" spans="1:10" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="212" t="s">
+      <c r="B80" s="227"/>
+      <c r="C80" s="227"/>
+      <c r="D80" s="227"/>
+      <c r="E80" s="227"/>
+      <c r="F80" s="227"/>
+      <c r="G80" s="227"/>
+      <c r="H80" s="142">
+        <f>H77+H74</f>
+        <v>4482071.49</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="178" t="s">
         <v>126</v>
       </c>
-      <c r="B82" s="213"/>
-      <c r="C82" s="213"/>
-      <c r="D82" s="213"/>
-      <c r="E82" s="213"/>
-      <c r="F82" s="213"/>
-      <c r="G82" s="213"/>
-      <c r="H82" s="142">
-        <f>H79+H76</f>
-        <v>4278048.5999999996</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="214" t="s">
+      <c r="B81" s="179"/>
+      <c r="C81" s="179"/>
+      <c r="D81" s="179"/>
+      <c r="E81" s="179"/>
+      <c r="F81" s="179"/>
+      <c r="G81" s="179"/>
+      <c r="H81" s="100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="101"/>
+      <c r="B82" s="101"/>
+      <c r="C82" s="101"/>
+      <c r="D82" s="101"/>
+      <c r="E82" s="101"/>
+      <c r="F82" s="101"/>
+      <c r="G82" s="101"/>
+      <c r="H82" s="102"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+    </row>
+    <row r="84" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A84" s="201" t="s">
         <v>127</v>
       </c>
-      <c r="B83" s="215"/>
-      <c r="C83" s="215"/>
-      <c r="D83" s="215"/>
-      <c r="E83" s="215"/>
-      <c r="F83" s="215"/>
-      <c r="G83" s="215"/>
-      <c r="H83" s="100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="101"/>
-      <c r="B84" s="101"/>
-      <c r="C84" s="101"/>
-      <c r="D84" s="101"/>
-      <c r="E84" s="101"/>
-      <c r="F84" s="101"/>
-      <c r="G84" s="101"/>
-      <c r="H84" s="102"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-    </row>
-    <row r="86" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A86" s="182" t="s">
+      <c r="B84" s="202"/>
+      <c r="C84" s="202"/>
+      <c r="D84" s="202"/>
+      <c r="E84" s="202"/>
+      <c r="F84" s="202"/>
+      <c r="G84" s="202"/>
+      <c r="H84" s="203"/>
+    </row>
+    <row r="85" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A85" s="103" t="s">
         <v>128</v>
       </c>
-      <c r="B86" s="183"/>
-      <c r="C86" s="183"/>
-      <c r="D86" s="183"/>
-      <c r="E86" s="183"/>
-      <c r="F86" s="183"/>
-      <c r="G86" s="183"/>
-      <c r="H86" s="184"/>
-    </row>
-    <row r="87" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A87" s="103" t="s">
+      <c r="B85" s="104"/>
+      <c r="C85" s="104"/>
+      <c r="D85" s="104"/>
+      <c r="E85" s="104"/>
+      <c r="F85" s="104"/>
+      <c r="G85" s="104"/>
+      <c r="H85" s="105">
+        <v>-11568.140593531542</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B87" s="104"/>
-      <c r="C87" s="104"/>
-      <c r="D87" s="104"/>
-      <c r="E87" s="104"/>
-      <c r="F87" s="104"/>
-      <c r="G87" s="104"/>
-      <c r="H87" s="105">
-        <v>-834604.30226353183</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="8" t="s">
+      <c r="B86" s="106"/>
+      <c r="C86" s="106"/>
+      <c r="D86" s="106"/>
+      <c r="E86" s="106"/>
+      <c r="F86" s="106"/>
+      <c r="G86" s="106"/>
+      <c r="H86" s="18">
+        <f>Planilla!G43</f>
+        <v>4887946</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="107" t="s">
+        <v>135</v>
+      </c>
+      <c r="B87" s="108"/>
+      <c r="C87" s="108"/>
+      <c r="D87" s="108"/>
+      <c r="E87" s="108"/>
+      <c r="F87" s="108"/>
+      <c r="G87" s="108"/>
+      <c r="H87" s="122">
+        <f>-H80</f>
+        <v>-4482071.49</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="107" t="s">
         <v>130</v>
       </c>
-      <c r="B88" s="106"/>
-      <c r="C88" s="106"/>
-      <c r="D88" s="106"/>
-      <c r="E88" s="106"/>
-      <c r="F88" s="106"/>
-      <c r="G88" s="106"/>
-      <c r="H88" s="18">
-        <f>Planilla!G43</f>
-        <v>5380591.9416700006</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B88" s="108"/>
+      <c r="C88" s="108"/>
+      <c r="D88" s="108"/>
+      <c r="E88" s="108"/>
+      <c r="F88" s="108"/>
+      <c r="G88" s="108"/>
+      <c r="H88" s="31">
+        <f>D103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="107" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="B89" s="108"/>
       <c r="C89" s="108"/>
@@ -5490,218 +5490,203 @@
       <c r="F89" s="108"/>
       <c r="G89" s="108"/>
       <c r="H89" s="122">
-        <f>-H82</f>
-        <v>-4278048.5999999996</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+        <v>-2874</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="107" t="s">
-        <v>131</v>
-      </c>
-      <c r="B90" s="108"/>
+        <v>151</v>
+      </c>
+      <c r="B90" s="109"/>
       <c r="C90" s="108"/>
       <c r="D90" s="108"/>
       <c r="E90" s="108"/>
       <c r="F90" s="108"/>
       <c r="G90" s="108"/>
-      <c r="H90" s="31">
-        <f>D105</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="107" t="s">
-        <v>169</v>
-      </c>
-      <c r="B91" s="108"/>
-      <c r="C91" s="108"/>
-      <c r="D91" s="108"/>
-      <c r="E91" s="108"/>
-      <c r="F91" s="108"/>
-      <c r="G91" s="108"/>
-      <c r="H91" s="122">
-        <f>-(3244+6707+6908+7115)</f>
-        <v>-23974</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A92" s="107" t="s">
-        <v>153</v>
-      </c>
-      <c r="B92" s="109"/>
-      <c r="C92" s="108"/>
-      <c r="D92" s="108"/>
-      <c r="E92" s="108"/>
-      <c r="F92" s="108"/>
-      <c r="G92" s="108"/>
-      <c r="H92" s="130">
-        <f>-H66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A93" s="110" t="s">
+      <c r="H90" s="130">
+        <f>-H64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A91" s="110" t="s">
+        <v>131</v>
+      </c>
+      <c r="B91" s="111"/>
+      <c r="C91" s="111"/>
+      <c r="D91" s="111"/>
+      <c r="E91" s="111"/>
+      <c r="F91" s="111"/>
+      <c r="G91" s="111"/>
+      <c r="H91" s="112">
+        <f>SUM(H85:H90)</f>
+        <v>391432.36940646823</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="93" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="204" t="s">
         <v>132</v>
       </c>
-      <c r="B93" s="111"/>
-      <c r="C93" s="111"/>
-      <c r="D93" s="111"/>
-      <c r="E93" s="111"/>
-      <c r="F93" s="111"/>
-      <c r="G93" s="111"/>
-      <c r="H93" s="112">
-        <f>SUM(H87:H92)</f>
-        <v>243965.03940646909</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="185" t="s">
-        <v>133</v>
-      </c>
-      <c r="B95" s="186"/>
-      <c r="C95" s="186"/>
-      <c r="D95" s="186"/>
-      <c r="E95" s="186"/>
-      <c r="F95" s="186"/>
-      <c r="G95" s="186"/>
-      <c r="H95" s="187"/>
-    </row>
-    <row r="96" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A96" s="113" t="s">
-        <v>129</v>
-      </c>
-      <c r="B96" s="113"/>
-      <c r="C96" s="113"/>
-      <c r="D96" s="113"/>
-      <c r="E96" s="113"/>
-      <c r="F96" s="113"/>
-      <c r="G96" s="113"/>
-      <c r="H96" s="114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B93" s="205"/>
+      <c r="C93" s="205"/>
+      <c r="D93" s="205"/>
+      <c r="E93" s="205"/>
+      <c r="F93" s="205"/>
+      <c r="G93" s="205"/>
+      <c r="H93" s="206"/>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="113" t="s">
+        <v>128</v>
+      </c>
+      <c r="B94" s="113"/>
+      <c r="C94" s="113"/>
+      <c r="D94" s="113"/>
+      <c r="E94" s="113"/>
+      <c r="F94" s="113"/>
+      <c r="G94" s="113"/>
+      <c r="H94" s="114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="6"/>
+      <c r="B95" s="115"/>
+      <c r="C95" s="108"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="18"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="6"/>
+      <c r="B96" s="116"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="18"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
-      <c r="B97" s="115"/>
-      <c r="C97" s="108"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="18"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="6"/>
-      <c r="B98" s="116"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="18"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="18"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="117" t="s">
-        <v>132</v>
-      </c>
-      <c r="B100" s="117"/>
-      <c r="C100" s="117"/>
-      <c r="D100" s="117"/>
-      <c r="E100" s="117"/>
-      <c r="F100" s="117"/>
-      <c r="G100" s="117"/>
-      <c r="H100" s="118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="124" t="s">
-        <v>145</v>
-      </c>
-      <c r="B102" s="125"/>
-      <c r="C102" s="125"/>
-      <c r="D102" s="125"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="18"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="18"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="119" t="s">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="B98" s="117"/>
+      <c r="C98" s="117"/>
+      <c r="D98" s="117"/>
+      <c r="E98" s="117"/>
+      <c r="F98" s="117"/>
+      <c r="G98" s="117"/>
+      <c r="H98" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B100" s="125"/>
+      <c r="C100" s="125"/>
+      <c r="D100" s="125"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="18"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="18"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="B105" s="125"/>
-      <c r="C105" s="125"/>
-      <c r="D105" s="135">
-        <f>SUM(D103:D104)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="124" t="s">
-        <v>146</v>
-      </c>
-      <c r="B107" s="119"/>
-      <c r="C107" s="119"/>
-      <c r="D107" s="119"/>
-    </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B103" s="125"/>
+      <c r="C103" s="125"/>
+      <c r="D103" s="135">
+        <f>SUM(D101:D102)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="124" t="s">
+        <v>144</v>
+      </c>
+      <c r="B105" s="119"/>
+      <c r="C105" s="119"/>
+      <c r="D105" s="119"/>
+    </row>
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="6"/>
+      <c r="B106" s="99"/>
+      <c r="C106" s="99"/>
+      <c r="D106" s="121"/>
+    </row>
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="126"/>
+    </row>
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
-      <c r="B108" s="99"/>
-      <c r="C108" s="99"/>
-      <c r="D108" s="121"/>
-    </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="126"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
       <c r="D109" s="126"/>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="126"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="126"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="120" t="s">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="B112" s="120"/>
-      <c r="C112" s="188">
-        <f>SUM(D108:D111)</f>
-        <v>0</v>
-      </c>
-      <c r="D112" s="189"/>
+      <c r="B110" s="120"/>
+      <c r="C110" s="207">
+        <f>SUM(D106:D109)</f>
+        <v>0</v>
+      </c>
+      <c r="D110" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="A84:H84"/>
+    <mergeCell ref="A93:H93"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A81:G81"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="E3:H3"/>
@@ -5710,29 +5695,13 @@
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="J40:J42"/>
-    <mergeCell ref="A86:H86"/>
-    <mergeCell ref="A95:H95"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A82:G82"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
